--- a/Update_2026-10-30/Margin_Check_vs_Cost.xlsx
+++ b/Update_2026-10-30/Margin_Check_vs_Cost.xlsx
@@ -7,10 +7,191 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Margin_cost_as_given" sheetId="1" r:id="rId1"/>
+    <sheet name="Both_cost_cases_min_price" sheetId="2" r:id="rId2"/>
+    <sheet name="Assumptions" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="58">
+  <si>
+    <t>Market</t>
+  </si>
+  <si>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>Cost_EUR</t>
+  </si>
+  <si>
+    <t>Sale_price</t>
+  </si>
+  <si>
+    <t>Sale_profit_EUR</t>
+  </si>
+  <si>
+    <t>Sale_margin%</t>
+  </si>
+  <si>
+    <t>T2_price</t>
+  </si>
+  <si>
+    <t>T2_profit_EUR</t>
+  </si>
+  <si>
+    <t>T2_margin%</t>
+  </si>
+  <si>
+    <t>T4_price</t>
+  </si>
+  <si>
+    <t>T4_profit_EUR</t>
+  </si>
+  <si>
+    <t>T4_margin%</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>2L-CFOT-WAF5</t>
+  </si>
+  <si>
+    <t>79-IMQK-CFL6</t>
+  </si>
+  <si>
+    <t>AL-OBXA-2JAB</t>
+  </si>
+  <si>
+    <t>BO-LDT0-9J23</t>
+  </si>
+  <si>
+    <t>O7-OU4A-2PTM</t>
+  </si>
+  <si>
+    <t>RY-63EN-QQ04</t>
+  </si>
+  <si>
+    <t>SO-33NV-Y8TE</t>
+  </si>
+  <si>
+    <t>WJ-9EH3-NUHN</t>
+  </si>
+  <si>
+    <t>47-TYVC-KKS9</t>
+  </si>
+  <si>
+    <t>5M-COWO-NTC4</t>
+  </si>
+  <si>
+    <t>MQ-GW44-AUVE</t>
+  </si>
+  <si>
+    <t>N4-FRNJ-Q53V</t>
+  </si>
+  <si>
+    <t>TG-5RTH-70GN</t>
+  </si>
+  <si>
+    <t>4751045860314_mfn</t>
+  </si>
+  <si>
+    <t>F8-4Y8G-GT5L</t>
+  </si>
+  <si>
+    <t>UX-E5I6-5O5L</t>
+  </si>
+  <si>
+    <t>DP-ZW1J-GZYS</t>
+  </si>
+  <si>
+    <t>2M-RLDD-XQAY</t>
+  </si>
+  <si>
+    <t>BF-UJUW-N586</t>
+  </si>
+  <si>
+    <t>YJ-OPSZ-IOCI</t>
+  </si>
+  <si>
+    <t>GO-HRO6-WM8V</t>
+  </si>
+  <si>
+    <t>H3-5FMC-FAD4</t>
+  </si>
+  <si>
+    <t>4751045863421_mfn</t>
+  </si>
+  <si>
+    <t>4751045863438_mfn</t>
+  </si>
+  <si>
+    <t>4751045863360_mfn</t>
+  </si>
+  <si>
+    <t>4751045863490_mfn</t>
+  </si>
+  <si>
+    <t>4751045860437_mfn</t>
+  </si>
+  <si>
+    <t>4751045860451_mfn</t>
+  </si>
+  <si>
+    <t>4751045860468_mfn</t>
+  </si>
+  <si>
+    <t>B8-S7B1-XUBY</t>
+  </si>
+  <si>
+    <t>R1-RAXF-Z5I9</t>
+  </si>
+  <si>
+    <t>ZX-GBC1-3353</t>
+  </si>
+  <si>
+    <t>PVN_deducted</t>
+  </si>
+  <si>
+    <t>Sale</t>
+  </si>
+  <si>
+    <t>T4</t>
+  </si>
+  <si>
+    <t>Margin_Sale</t>
+  </si>
+  <si>
+    <t>Margin_T4</t>
+  </si>
+  <si>
+    <t>Min_Sale_for_20pct_at_T4</t>
+  </si>
+  <si>
+    <t>Assumption</t>
+  </si>
+  <si>
+    <t>Cost = 'Закуп + доставка до Риги + PVN' from the Google sheet (EUR), same value for UK and DE; 8 new SKUs from tab 'Ввод в ассортимент' column eur.</t>
+  </si>
+  <si>
+    <t>Margin = (net price ex VAT - Amazon referral fee - cost) / net price; shipping Latvia-&gt;UK/DE, ads, returns NOT included.</t>
+  </si>
+  <si>
+    <t>VAT: UK 20%, DE 19%. Referral fee: 8% if gross price &lt;= 10, else 15% (Beauty). Verify with your fee schedule.</t>
+  </si>
+  <si>
+    <t>GBP-&gt;EUR 1.15 (assumption).</t>
+  </si>
+  <si>
+    <t>Case PVN_deducted = cost / 1.21 (Latvian VAT recoverable).</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -340,9 +521,6271 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>3.87</v>
+      </c>
+      <c r="D2">
+        <v>11.99</v>
+      </c>
+      <c r="E2">
+        <v>5.55</v>
+      </c>
+      <c r="F2">
+        <v>48.3</v>
+      </c>
+      <c r="G2">
+        <v>11.39</v>
+      </c>
+      <c r="H2">
+        <v>5.08</v>
+      </c>
+      <c r="I2">
+        <v>46.5</v>
+      </c>
+      <c r="J2">
+        <v>10.79</v>
+      </c>
+      <c r="K2">
+        <v>4.61</v>
+      </c>
+      <c r="L2">
+        <v>44.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>3.87</v>
+      </c>
+      <c r="D3">
+        <v>19.99</v>
+      </c>
+      <c r="E3">
+        <v>11.84</v>
+      </c>
+      <c r="F3">
+        <v>61.8</v>
+      </c>
+      <c r="G3">
+        <v>18.99</v>
+      </c>
+      <c r="H3">
+        <v>11.05</v>
+      </c>
+      <c r="I3">
+        <v>60.7</v>
+      </c>
+      <c r="J3">
+        <v>17.99</v>
+      </c>
+      <c r="K3">
+        <v>10.27</v>
+      </c>
+      <c r="L3">
+        <v>59.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <v>3.87</v>
+      </c>
+      <c r="D4">
+        <v>19.99</v>
+      </c>
+      <c r="E4">
+        <v>11.84</v>
+      </c>
+      <c r="F4">
+        <v>61.8</v>
+      </c>
+      <c r="G4">
+        <v>18.99</v>
+      </c>
+      <c r="H4">
+        <v>11.05</v>
+      </c>
+      <c r="I4">
+        <v>60.7</v>
+      </c>
+      <c r="J4">
+        <v>17.99</v>
+      </c>
+      <c r="K4">
+        <v>10.27</v>
+      </c>
+      <c r="L4">
+        <v>59.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5">
+        <v>3.87</v>
+      </c>
+      <c r="D5">
+        <v>19.99</v>
+      </c>
+      <c r="E5">
+        <v>11.84</v>
+      </c>
+      <c r="F5">
+        <v>61.8</v>
+      </c>
+      <c r="G5">
+        <v>18.99</v>
+      </c>
+      <c r="H5">
+        <v>11.05</v>
+      </c>
+      <c r="I5">
+        <v>60.7</v>
+      </c>
+      <c r="J5">
+        <v>17.99</v>
+      </c>
+      <c r="K5">
+        <v>10.27</v>
+      </c>
+      <c r="L5">
+        <v>59.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6">
+        <v>3.87</v>
+      </c>
+      <c r="D6">
+        <v>19.99</v>
+      </c>
+      <c r="E6">
+        <v>11.84</v>
+      </c>
+      <c r="F6">
+        <v>61.8</v>
+      </c>
+      <c r="G6">
+        <v>18.99</v>
+      </c>
+      <c r="H6">
+        <v>11.05</v>
+      </c>
+      <c r="I6">
+        <v>60.7</v>
+      </c>
+      <c r="J6">
+        <v>17.99</v>
+      </c>
+      <c r="K6">
+        <v>10.27</v>
+      </c>
+      <c r="L6">
+        <v>59.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>3.87</v>
+      </c>
+      <c r="D7">
+        <v>19.99</v>
+      </c>
+      <c r="E7">
+        <v>11.84</v>
+      </c>
+      <c r="F7">
+        <v>61.8</v>
+      </c>
+      <c r="G7">
+        <v>18.99</v>
+      </c>
+      <c r="H7">
+        <v>11.05</v>
+      </c>
+      <c r="I7">
+        <v>60.7</v>
+      </c>
+      <c r="J7">
+        <v>17.99</v>
+      </c>
+      <c r="K7">
+        <v>10.27</v>
+      </c>
+      <c r="L7">
+        <v>59.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>3.87</v>
+      </c>
+      <c r="D8">
+        <v>19.99</v>
+      </c>
+      <c r="E8">
+        <v>11.84</v>
+      </c>
+      <c r="F8">
+        <v>61.8</v>
+      </c>
+      <c r="G8">
+        <v>18.99</v>
+      </c>
+      <c r="H8">
+        <v>11.05</v>
+      </c>
+      <c r="I8">
+        <v>60.7</v>
+      </c>
+      <c r="J8">
+        <v>17.99</v>
+      </c>
+      <c r="K8">
+        <v>10.27</v>
+      </c>
+      <c r="L8">
+        <v>59.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9">
+        <v>3.87</v>
+      </c>
+      <c r="D9">
+        <v>11.99</v>
+      </c>
+      <c r="E9">
+        <v>5.55</v>
+      </c>
+      <c r="F9">
+        <v>48.3</v>
+      </c>
+      <c r="G9">
+        <v>11.39</v>
+      </c>
+      <c r="H9">
+        <v>5.08</v>
+      </c>
+      <c r="I9">
+        <v>46.5</v>
+      </c>
+      <c r="J9">
+        <v>10.79</v>
+      </c>
+      <c r="K9">
+        <v>4.61</v>
+      </c>
+      <c r="L9">
+        <v>44.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10">
+        <v>14.76</v>
+      </c>
+      <c r="D10">
+        <v>54.99</v>
+      </c>
+      <c r="E10">
+        <v>28.45</v>
+      </c>
+      <c r="F10">
+        <v>54</v>
+      </c>
+      <c r="G10">
+        <v>52.24</v>
+      </c>
+      <c r="H10">
+        <v>26.29</v>
+      </c>
+      <c r="I10">
+        <v>52.5</v>
+      </c>
+      <c r="J10">
+        <v>49.49</v>
+      </c>
+      <c r="K10">
+        <v>24.13</v>
+      </c>
+      <c r="L10">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11">
+        <v>14.62</v>
+      </c>
+      <c r="D11">
+        <v>52.99</v>
+      </c>
+      <c r="E11">
+        <v>27.02</v>
+      </c>
+      <c r="F11">
+        <v>53.2</v>
+      </c>
+      <c r="G11">
+        <v>50.34</v>
+      </c>
+      <c r="H11">
+        <v>24.94</v>
+      </c>
+      <c r="I11">
+        <v>51.7</v>
+      </c>
+      <c r="J11">
+        <v>47.69</v>
+      </c>
+      <c r="K11">
+        <v>22.86</v>
+      </c>
+      <c r="L11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12">
+        <v>14.68</v>
+      </c>
+      <c r="D12">
+        <v>52.99</v>
+      </c>
+      <c r="E12">
+        <v>26.96</v>
+      </c>
+      <c r="F12">
+        <v>53.1</v>
+      </c>
+      <c r="G12">
+        <v>50.34</v>
+      </c>
+      <c r="H12">
+        <v>24.88</v>
+      </c>
+      <c r="I12">
+        <v>51.6</v>
+      </c>
+      <c r="J12">
+        <v>47.69</v>
+      </c>
+      <c r="K12">
+        <v>22.8</v>
+      </c>
+      <c r="L12">
+        <v>49.9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13">
+        <v>7.81</v>
+      </c>
+      <c r="D13">
+        <v>24.99</v>
+      </c>
+      <c r="E13">
+        <v>11.83</v>
+      </c>
+      <c r="F13">
+        <v>49.4</v>
+      </c>
+      <c r="G13">
+        <v>23.74</v>
+      </c>
+      <c r="H13">
+        <v>10.85</v>
+      </c>
+      <c r="I13">
+        <v>47.7</v>
+      </c>
+      <c r="J13">
+        <v>22.49</v>
+      </c>
+      <c r="K13">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="L13">
+        <v>45.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14">
+        <v>7.81</v>
+      </c>
+      <c r="D14">
+        <v>27.99</v>
+      </c>
+      <c r="E14">
+        <v>14.19</v>
+      </c>
+      <c r="F14">
+        <v>52.9</v>
+      </c>
+      <c r="G14">
+        <v>26.59</v>
+      </c>
+      <c r="H14">
+        <v>13.09</v>
+      </c>
+      <c r="I14">
+        <v>51.4</v>
+      </c>
+      <c r="J14">
+        <v>25.19</v>
+      </c>
+      <c r="K14">
+        <v>11.99</v>
+      </c>
+      <c r="L14">
+        <v>49.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15">
+        <v>3.03</v>
+      </c>
+      <c r="D15">
+        <v>3.68</v>
+      </c>
+      <c r="E15">
+        <v>0.16</v>
+      </c>
+      <c r="F15">
+        <v>4.5</v>
+      </c>
+      <c r="G15">
+        <v>3.5</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0.1</v>
+      </c>
+      <c r="J15">
+        <v>3.31</v>
+      </c>
+      <c r="K15">
+        <v>-0.16</v>
+      </c>
+      <c r="L15">
+        <v>-5.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16">
+        <v>11.07</v>
+      </c>
+      <c r="D16">
+        <v>35.99</v>
+      </c>
+      <c r="E16">
+        <v>17.21</v>
+      </c>
+      <c r="F16">
+        <v>49.9</v>
+      </c>
+      <c r="G16">
+        <v>34.19</v>
+      </c>
+      <c r="H16">
+        <v>15.8</v>
+      </c>
+      <c r="I16">
+        <v>48.2</v>
+      </c>
+      <c r="J16">
+        <v>32.39</v>
+      </c>
+      <c r="K16">
+        <v>14.38</v>
+      </c>
+      <c r="L16">
+        <v>46.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17">
+        <v>11.07</v>
+      </c>
+      <c r="D17">
+        <v>35.99</v>
+      </c>
+      <c r="E17">
+        <v>17.21</v>
+      </c>
+      <c r="F17">
+        <v>49.9</v>
+      </c>
+      <c r="G17">
+        <v>34.19</v>
+      </c>
+      <c r="H17">
+        <v>15.8</v>
+      </c>
+      <c r="I17">
+        <v>48.2</v>
+      </c>
+      <c r="J17">
+        <v>32.39</v>
+      </c>
+      <c r="K17">
+        <v>14.38</v>
+      </c>
+      <c r="L17">
+        <v>46.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18">
+        <v>7.63</v>
+      </c>
+      <c r="D18">
+        <v>25.99</v>
+      </c>
+      <c r="E18">
+        <v>12.79</v>
+      </c>
+      <c r="F18">
+        <v>51.4</v>
+      </c>
+      <c r="G18">
+        <v>24.69</v>
+      </c>
+      <c r="H18">
+        <v>11.77</v>
+      </c>
+      <c r="I18">
+        <v>49.8</v>
+      </c>
+      <c r="J18">
+        <v>23.39</v>
+      </c>
+      <c r="K18">
+        <v>10.75</v>
+      </c>
+      <c r="L18">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="D19">
+        <v>27.99</v>
+      </c>
+      <c r="E19">
+        <v>13.12</v>
+      </c>
+      <c r="F19">
+        <v>48.9</v>
+      </c>
+      <c r="G19">
+        <v>26.59</v>
+      </c>
+      <c r="H19">
+        <v>12.02</v>
+      </c>
+      <c r="I19">
+        <v>47.2</v>
+      </c>
+      <c r="J19">
+        <v>25.19</v>
+      </c>
+      <c r="K19">
+        <v>10.92</v>
+      </c>
+      <c r="L19">
+        <v>45.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20">
+        <v>12.1</v>
+      </c>
+      <c r="D20">
+        <v>45.99</v>
+      </c>
+      <c r="E20">
+        <v>24.04</v>
+      </c>
+      <c r="F20">
+        <v>54.5</v>
+      </c>
+      <c r="G20">
+        <v>43.69</v>
+      </c>
+      <c r="H20">
+        <v>22.23</v>
+      </c>
+      <c r="I20">
+        <v>53.1</v>
+      </c>
+      <c r="J20">
+        <v>41.39</v>
+      </c>
+      <c r="K20">
+        <v>20.43</v>
+      </c>
+      <c r="L20">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="D21">
+        <v>27.99</v>
+      </c>
+      <c r="E21">
+        <v>13.12</v>
+      </c>
+      <c r="F21">
+        <v>48.9</v>
+      </c>
+      <c r="G21">
+        <v>26.59</v>
+      </c>
+      <c r="H21">
+        <v>12.02</v>
+      </c>
+      <c r="I21">
+        <v>47.2</v>
+      </c>
+      <c r="J21">
+        <v>25.19</v>
+      </c>
+      <c r="K21">
+        <v>10.92</v>
+      </c>
+      <c r="L21">
+        <v>45.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22">
+        <v>8.85</v>
+      </c>
+      <c r="D22">
+        <v>29.99</v>
+      </c>
+      <c r="E22">
+        <v>14.72</v>
+      </c>
+      <c r="F22">
+        <v>51.2</v>
+      </c>
+      <c r="G22">
+        <v>28.49</v>
+      </c>
+      <c r="H22">
+        <v>13.54</v>
+      </c>
+      <c r="I22">
+        <v>49.6</v>
+      </c>
+      <c r="J22">
+        <v>26.99</v>
+      </c>
+      <c r="K22">
+        <v>12.36</v>
+      </c>
+      <c r="L22">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23">
+        <v>6.91</v>
+      </c>
+      <c r="D23">
+        <v>29.99</v>
+      </c>
+      <c r="E23">
+        <v>16.66</v>
+      </c>
+      <c r="F23">
+        <v>58</v>
+      </c>
+      <c r="G23">
+        <v>28.49</v>
+      </c>
+      <c r="H23">
+        <v>15.48</v>
+      </c>
+      <c r="I23">
+        <v>56.7</v>
+      </c>
+      <c r="J23">
+        <v>26.99</v>
+      </c>
+      <c r="K23">
+        <v>14.3</v>
+      </c>
+      <c r="L23">
+        <v>55.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24">
+        <v>6.26</v>
+      </c>
+      <c r="D24">
+        <v>7.6</v>
+      </c>
+      <c r="E24">
+        <v>0.32</v>
+      </c>
+      <c r="F24">
+        <v>4.5</v>
+      </c>
+      <c r="G24">
+        <v>7.22</v>
+      </c>
+      <c r="H24">
+        <v>-0.01</v>
+      </c>
+      <c r="I24">
+        <v>-0.1</v>
+      </c>
+      <c r="J24">
+        <v>6.84</v>
+      </c>
+      <c r="K24">
+        <v>-0.33</v>
+      </c>
+      <c r="L24">
+        <v>-5.1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25">
+        <v>19.72</v>
+      </c>
+      <c r="D25">
+        <v>23.92</v>
+      </c>
+      <c r="E25">
+        <v>-0.92</v>
+      </c>
+      <c r="F25">
+        <v>-4</v>
+      </c>
+      <c r="G25">
+        <v>22.72</v>
+      </c>
+      <c r="H25">
+        <v>-1.87</v>
+      </c>
+      <c r="I25">
+        <v>-8.6</v>
+      </c>
+      <c r="J25">
+        <v>21.53</v>
+      </c>
+      <c r="K25">
+        <v>-2.8</v>
+      </c>
+      <c r="L25">
+        <v>-13.6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26">
+        <v>6.26</v>
+      </c>
+      <c r="D26">
+        <v>7.6</v>
+      </c>
+      <c r="E26">
+        <v>0.32</v>
+      </c>
+      <c r="F26">
+        <v>4.5</v>
+      </c>
+      <c r="G26">
+        <v>7.22</v>
+      </c>
+      <c r="H26">
+        <v>-0.01</v>
+      </c>
+      <c r="I26">
+        <v>-0.1</v>
+      </c>
+      <c r="J26">
+        <v>6.84</v>
+      </c>
+      <c r="K26">
+        <v>-0.33</v>
+      </c>
+      <c r="L26">
+        <v>-5.1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27">
+        <v>19.72</v>
+      </c>
+      <c r="D27">
+        <v>23.92</v>
+      </c>
+      <c r="E27">
+        <v>-0.92</v>
+      </c>
+      <c r="F27">
+        <v>-4</v>
+      </c>
+      <c r="G27">
+        <v>22.72</v>
+      </c>
+      <c r="H27">
+        <v>-1.87</v>
+      </c>
+      <c r="I27">
+        <v>-8.6</v>
+      </c>
+      <c r="J27">
+        <v>21.53</v>
+      </c>
+      <c r="K27">
+        <v>-2.8</v>
+      </c>
+      <c r="L27">
+        <v>-13.6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28">
+        <v>6.78</v>
+      </c>
+      <c r="D28">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="E28">
+        <v>0.34</v>
+      </c>
+      <c r="F28">
+        <v>4.3</v>
+      </c>
+      <c r="G28">
+        <v>7.81</v>
+      </c>
+      <c r="H28">
+        <v>-0.01</v>
+      </c>
+      <c r="I28">
+        <v>-0.2</v>
+      </c>
+      <c r="J28">
+        <v>7.4</v>
+      </c>
+      <c r="K28">
+        <v>-0.37</v>
+      </c>
+      <c r="L28">
+        <v>-5.2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29">
+        <v>2.5</v>
+      </c>
+      <c r="D29">
+        <v>3.03</v>
+      </c>
+      <c r="E29">
+        <v>0.12</v>
+      </c>
+      <c r="F29">
+        <v>4.3</v>
+      </c>
+      <c r="G29">
+        <v>2.88</v>
+      </c>
+      <c r="H29">
+        <v>-0</v>
+      </c>
+      <c r="I29">
+        <v>-0.2</v>
+      </c>
+      <c r="J29">
+        <v>2.73</v>
+      </c>
+      <c r="K29">
+        <v>-0.13</v>
+      </c>
+      <c r="L29">
+        <v>-5.2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30">
+        <v>6.55</v>
+      </c>
+      <c r="D30">
+        <v>7.94</v>
+      </c>
+      <c r="E30">
+        <v>0.33</v>
+      </c>
+      <c r="F30">
+        <v>4.3</v>
+      </c>
+      <c r="G30">
+        <v>7.54</v>
+      </c>
+      <c r="H30">
+        <v>-0.02</v>
+      </c>
+      <c r="I30">
+        <v>-0.2</v>
+      </c>
+      <c r="J30">
+        <v>7.15</v>
+      </c>
+      <c r="K30">
+        <v>-0.36</v>
+      </c>
+      <c r="L30">
+        <v>-5.2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31">
+        <v>9.92</v>
+      </c>
+      <c r="D31">
+        <v>29.99</v>
+      </c>
+      <c r="E31">
+        <v>13.65</v>
+      </c>
+      <c r="F31">
+        <v>47.5</v>
+      </c>
+      <c r="G31">
+        <v>28.49</v>
+      </c>
+      <c r="H31">
+        <v>12.47</v>
+      </c>
+      <c r="I31">
+        <v>45.7</v>
+      </c>
+      <c r="J31">
+        <v>26.99</v>
+      </c>
+      <c r="K31">
+        <v>11.29</v>
+      </c>
+      <c r="L31">
+        <v>43.6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32">
+        <v>3</v>
+      </c>
+      <c r="D32">
+        <v>21.99</v>
+      </c>
+      <c r="E32">
+        <v>14.28</v>
+      </c>
+      <c r="F32">
+        <v>67.8</v>
+      </c>
+      <c r="G32">
+        <v>20.89</v>
+      </c>
+      <c r="H32">
+        <v>13.42</v>
+      </c>
+      <c r="I32">
+        <v>67</v>
+      </c>
+      <c r="J32">
+        <v>19.79</v>
+      </c>
+      <c r="K32">
+        <v>12.55</v>
+      </c>
+      <c r="L32">
+        <v>66.2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33">
+        <v>7.98</v>
+      </c>
+      <c r="D33">
+        <v>28.99</v>
+      </c>
+      <c r="E33">
+        <v>14.8</v>
+      </c>
+      <c r="F33">
+        <v>53.3</v>
+      </c>
+      <c r="G33">
+        <v>27.54</v>
+      </c>
+      <c r="H33">
+        <v>13.66</v>
+      </c>
+      <c r="I33">
+        <v>51.8</v>
+      </c>
+      <c r="J33">
+        <v>26.09</v>
+      </c>
+      <c r="K33">
+        <v>12.52</v>
+      </c>
+      <c r="L33">
+        <v>50.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34">
+        <v>3.87</v>
+      </c>
+      <c r="D34">
+        <v>14.27</v>
+      </c>
+      <c r="E34">
+        <v>5.98</v>
+      </c>
+      <c r="F34">
+        <v>49.9</v>
+      </c>
+      <c r="G34">
+        <v>13.56</v>
+      </c>
+      <c r="H34">
+        <v>5.49</v>
+      </c>
+      <c r="I34">
+        <v>48.2</v>
+      </c>
+      <c r="J34">
+        <v>12.84</v>
+      </c>
+      <c r="K34">
+        <v>4.99</v>
+      </c>
+      <c r="L34">
+        <v>46.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35">
+        <v>3.87</v>
+      </c>
+      <c r="D35">
+        <v>23.79</v>
+      </c>
+      <c r="E35">
+        <v>12.55</v>
+      </c>
+      <c r="F35">
+        <v>62.8</v>
+      </c>
+      <c r="G35">
+        <v>22.6</v>
+      </c>
+      <c r="H35">
+        <v>11.73</v>
+      </c>
+      <c r="I35">
+        <v>61.8</v>
+      </c>
+      <c r="J35">
+        <v>21.41</v>
+      </c>
+      <c r="K35">
+        <v>10.91</v>
+      </c>
+      <c r="L35">
+        <v>60.6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36">
+        <v>3.87</v>
+      </c>
+      <c r="D36">
+        <v>23.79</v>
+      </c>
+      <c r="E36">
+        <v>12.55</v>
+      </c>
+      <c r="F36">
+        <v>62.8</v>
+      </c>
+      <c r="G36">
+        <v>22.6</v>
+      </c>
+      <c r="H36">
+        <v>11.73</v>
+      </c>
+      <c r="I36">
+        <v>61.8</v>
+      </c>
+      <c r="J36">
+        <v>21.41</v>
+      </c>
+      <c r="K36">
+        <v>10.91</v>
+      </c>
+      <c r="L36">
+        <v>60.6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" t="s">
+        <v>13</v>
+      </c>
+      <c r="B37" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37">
+        <v>3.87</v>
+      </c>
+      <c r="D37">
+        <v>23.79</v>
+      </c>
+      <c r="E37">
+        <v>12.55</v>
+      </c>
+      <c r="F37">
+        <v>62.8</v>
+      </c>
+      <c r="G37">
+        <v>22.6</v>
+      </c>
+      <c r="H37">
+        <v>11.73</v>
+      </c>
+      <c r="I37">
+        <v>61.8</v>
+      </c>
+      <c r="J37">
+        <v>21.41</v>
+      </c>
+      <c r="K37">
+        <v>10.91</v>
+      </c>
+      <c r="L37">
+        <v>60.6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38">
+        <v>3.87</v>
+      </c>
+      <c r="D38">
+        <v>23.79</v>
+      </c>
+      <c r="E38">
+        <v>12.55</v>
+      </c>
+      <c r="F38">
+        <v>62.8</v>
+      </c>
+      <c r="G38">
+        <v>22.6</v>
+      </c>
+      <c r="H38">
+        <v>11.73</v>
+      </c>
+      <c r="I38">
+        <v>61.8</v>
+      </c>
+      <c r="J38">
+        <v>21.41</v>
+      </c>
+      <c r="K38">
+        <v>10.91</v>
+      </c>
+      <c r="L38">
+        <v>60.6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39">
+        <v>3.87</v>
+      </c>
+      <c r="D39">
+        <v>23.79</v>
+      </c>
+      <c r="E39">
+        <v>12.55</v>
+      </c>
+      <c r="F39">
+        <v>62.8</v>
+      </c>
+      <c r="G39">
+        <v>22.6</v>
+      </c>
+      <c r="H39">
+        <v>11.73</v>
+      </c>
+      <c r="I39">
+        <v>61.8</v>
+      </c>
+      <c r="J39">
+        <v>21.41</v>
+      </c>
+      <c r="K39">
+        <v>10.91</v>
+      </c>
+      <c r="L39">
+        <v>60.6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40">
+        <v>3.87</v>
+      </c>
+      <c r="D40">
+        <v>23.79</v>
+      </c>
+      <c r="E40">
+        <v>12.55</v>
+      </c>
+      <c r="F40">
+        <v>62.8</v>
+      </c>
+      <c r="G40">
+        <v>22.6</v>
+      </c>
+      <c r="H40">
+        <v>11.73</v>
+      </c>
+      <c r="I40">
+        <v>61.8</v>
+      </c>
+      <c r="J40">
+        <v>21.41</v>
+      </c>
+      <c r="K40">
+        <v>10.91</v>
+      </c>
+      <c r="L40">
+        <v>60.6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41">
+        <v>3.87</v>
+      </c>
+      <c r="D41">
+        <v>14.27</v>
+      </c>
+      <c r="E41">
+        <v>5.98</v>
+      </c>
+      <c r="F41">
+        <v>49.9</v>
+      </c>
+      <c r="G41">
+        <v>13.56</v>
+      </c>
+      <c r="H41">
+        <v>5.49</v>
+      </c>
+      <c r="I41">
+        <v>48.2</v>
+      </c>
+      <c r="J41">
+        <v>12.84</v>
+      </c>
+      <c r="K41">
+        <v>4.99</v>
+      </c>
+      <c r="L41">
+        <v>46.3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" t="s">
+        <v>13</v>
+      </c>
+      <c r="B42" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42">
+        <v>14.76</v>
+      </c>
+      <c r="D42">
+        <v>63.55</v>
+      </c>
+      <c r="E42">
+        <v>29.11</v>
+      </c>
+      <c r="F42">
+        <v>54.5</v>
+      </c>
+      <c r="G42">
+        <v>60.37</v>
+      </c>
+      <c r="H42">
+        <v>26.92</v>
+      </c>
+      <c r="I42">
+        <v>53.1</v>
+      </c>
+      <c r="J42">
+        <v>57.2</v>
+      </c>
+      <c r="K42">
+        <v>24.73</v>
+      </c>
+      <c r="L42">
+        <v>51.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43">
+        <v>14.62</v>
+      </c>
+      <c r="D43">
+        <v>61.24</v>
+      </c>
+      <c r="E43">
+        <v>27.66</v>
+      </c>
+      <c r="F43">
+        <v>53.7</v>
+      </c>
+      <c r="G43">
+        <v>58.18</v>
+      </c>
+      <c r="H43">
+        <v>25.54</v>
+      </c>
+      <c r="I43">
+        <v>52.2</v>
+      </c>
+      <c r="J43">
+        <v>55.12</v>
+      </c>
+      <c r="K43">
+        <v>23.43</v>
+      </c>
+      <c r="L43">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44">
+        <v>14.68</v>
+      </c>
+      <c r="D44">
+        <v>61.24</v>
+      </c>
+      <c r="E44">
+        <v>27.6</v>
+      </c>
+      <c r="F44">
+        <v>53.6</v>
+      </c>
+      <c r="G44">
+        <v>58.18</v>
+      </c>
+      <c r="H44">
+        <v>25.48</v>
+      </c>
+      <c r="I44">
+        <v>52.1</v>
+      </c>
+      <c r="J44">
+        <v>55.12</v>
+      </c>
+      <c r="K44">
+        <v>23.37</v>
+      </c>
+      <c r="L44">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B45" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45">
+        <v>7.81</v>
+      </c>
+      <c r="D45">
+        <v>29.74</v>
+      </c>
+      <c r="E45">
+        <v>12.72</v>
+      </c>
+      <c r="F45">
+        <v>50.9</v>
+      </c>
+      <c r="G45">
+        <v>28.25</v>
+      </c>
+      <c r="H45">
+        <v>11.69</v>
+      </c>
+      <c r="I45">
+        <v>49.3</v>
+      </c>
+      <c r="J45">
+        <v>26.77</v>
+      </c>
+      <c r="K45">
+        <v>10.67</v>
+      </c>
+      <c r="L45">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46">
+        <v>7.81</v>
+      </c>
+      <c r="D46">
+        <v>33.31</v>
+      </c>
+      <c r="E46">
+        <v>15.19</v>
+      </c>
+      <c r="F46">
+        <v>54.2</v>
+      </c>
+      <c r="G46">
+        <v>31.64</v>
+      </c>
+      <c r="H46">
+        <v>14.03</v>
+      </c>
+      <c r="I46">
+        <v>52.8</v>
+      </c>
+      <c r="J46">
+        <v>29.98</v>
+      </c>
+      <c r="K46">
+        <v>12.89</v>
+      </c>
+      <c r="L46">
+        <v>51.1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47">
+        <v>3.03</v>
+      </c>
+      <c r="D47">
+        <v>4.38</v>
+      </c>
+      <c r="E47">
+        <v>0.3</v>
+      </c>
+      <c r="F47">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G47">
+        <v>4.16</v>
+      </c>
+      <c r="H47">
+        <v>0.13</v>
+      </c>
+      <c r="I47">
+        <v>3.8</v>
+      </c>
+      <c r="J47">
+        <v>3.94</v>
+      </c>
+      <c r="K47">
+        <v>-0.03</v>
+      </c>
+      <c r="L47">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48" t="s">
+        <v>28</v>
+      </c>
+      <c r="C48">
+        <v>11.07</v>
+      </c>
+      <c r="D48">
+        <v>42.83</v>
+      </c>
+      <c r="E48">
+        <v>18.5</v>
+      </c>
+      <c r="F48">
+        <v>51.4</v>
+      </c>
+      <c r="G48">
+        <v>40.69</v>
+      </c>
+      <c r="H48">
+        <v>17.02</v>
+      </c>
+      <c r="I48">
+        <v>49.8</v>
+      </c>
+      <c r="J48">
+        <v>38.55</v>
+      </c>
+      <c r="K48">
+        <v>15.54</v>
+      </c>
+      <c r="L48">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" t="s">
+        <v>13</v>
+      </c>
+      <c r="B49" t="s">
+        <v>29</v>
+      </c>
+      <c r="C49">
+        <v>11.07</v>
+      </c>
+      <c r="D49">
+        <v>42.83</v>
+      </c>
+      <c r="E49">
+        <v>18.5</v>
+      </c>
+      <c r="F49">
+        <v>51.4</v>
+      </c>
+      <c r="G49">
+        <v>40.69</v>
+      </c>
+      <c r="H49">
+        <v>17.02</v>
+      </c>
+      <c r="I49">
+        <v>49.8</v>
+      </c>
+      <c r="J49">
+        <v>38.55</v>
+      </c>
+      <c r="K49">
+        <v>15.54</v>
+      </c>
+      <c r="L49">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" t="s">
+        <v>13</v>
+      </c>
+      <c r="B50" t="s">
+        <v>30</v>
+      </c>
+      <c r="C50">
+        <v>7.63</v>
+      </c>
+      <c r="D50">
+        <v>30.93</v>
+      </c>
+      <c r="E50">
+        <v>13.72</v>
+      </c>
+      <c r="F50">
+        <v>52.8</v>
+      </c>
+      <c r="G50">
+        <v>29.38</v>
+      </c>
+      <c r="H50">
+        <v>12.65</v>
+      </c>
+      <c r="I50">
+        <v>51.2</v>
+      </c>
+      <c r="J50">
+        <v>27.84</v>
+      </c>
+      <c r="K50">
+        <v>11.59</v>
+      </c>
+      <c r="L50">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" t="s">
+        <v>13</v>
+      </c>
+      <c r="B51" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="D51">
+        <v>37.88</v>
+      </c>
+      <c r="E51">
+        <v>17.27</v>
+      </c>
+      <c r="F51">
+        <v>54.3</v>
+      </c>
+      <c r="G51">
+        <v>35.99</v>
+      </c>
+      <c r="H51">
+        <v>15.97</v>
+      </c>
+      <c r="I51">
+        <v>52.8</v>
+      </c>
+      <c r="J51">
+        <v>34.09</v>
+      </c>
+      <c r="K51">
+        <v>14.65</v>
+      </c>
+      <c r="L51">
+        <v>51.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" t="s">
+        <v>13</v>
+      </c>
+      <c r="B52" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52">
+        <v>12.1</v>
+      </c>
+      <c r="D52">
+        <v>54.73</v>
+      </c>
+      <c r="E52">
+        <v>25.68</v>
+      </c>
+      <c r="F52">
+        <v>55.8</v>
+      </c>
+      <c r="G52">
+        <v>51.99</v>
+      </c>
+      <c r="H52">
+        <v>23.79</v>
+      </c>
+      <c r="I52">
+        <v>54.5</v>
+      </c>
+      <c r="J52">
+        <v>49.26</v>
+      </c>
+      <c r="K52">
+        <v>21.91</v>
+      </c>
+      <c r="L52">
+        <v>52.9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" t="s">
+        <v>13</v>
+      </c>
+      <c r="B53" t="s">
+        <v>33</v>
+      </c>
+      <c r="C53">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="D53">
+        <v>33.31</v>
+      </c>
+      <c r="E53">
+        <v>14.12</v>
+      </c>
+      <c r="F53">
+        <v>50.4</v>
+      </c>
+      <c r="G53">
+        <v>31.64</v>
+      </c>
+      <c r="H53">
+        <v>12.96</v>
+      </c>
+      <c r="I53">
+        <v>48.8</v>
+      </c>
+      <c r="J53">
+        <v>29.98</v>
+      </c>
+      <c r="K53">
+        <v>11.82</v>
+      </c>
+      <c r="L53">
+        <v>46.9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" t="s">
+        <v>13</v>
+      </c>
+      <c r="B54" t="s">
+        <v>34</v>
+      </c>
+      <c r="C54">
+        <v>8.85</v>
+      </c>
+      <c r="D54">
+        <v>35.69</v>
+      </c>
+      <c r="E54">
+        <v>15.79</v>
+      </c>
+      <c r="F54">
+        <v>52.6</v>
+      </c>
+      <c r="G54">
+        <v>33.91</v>
+      </c>
+      <c r="H54">
+        <v>14.56</v>
+      </c>
+      <c r="I54">
+        <v>51.1</v>
+      </c>
+      <c r="J54">
+        <v>32.12</v>
+      </c>
+      <c r="K54">
+        <v>13.32</v>
+      </c>
+      <c r="L54">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" t="s">
+        <v>35</v>
+      </c>
+      <c r="C55">
+        <v>6.91</v>
+      </c>
+      <c r="D55">
+        <v>35.69</v>
+      </c>
+      <c r="E55">
+        <v>17.73</v>
+      </c>
+      <c r="F55">
+        <v>59.1</v>
+      </c>
+      <c r="G55">
+        <v>33.91</v>
+      </c>
+      <c r="H55">
+        <v>16.5</v>
+      </c>
+      <c r="I55">
+        <v>57.9</v>
+      </c>
+      <c r="J55">
+        <v>32.12</v>
+      </c>
+      <c r="K55">
+        <v>15.26</v>
+      </c>
+      <c r="L55">
+        <v>56.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B56" t="s">
+        <v>36</v>
+      </c>
+      <c r="C56">
+        <v>6.26</v>
+      </c>
+      <c r="D56">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="E56">
+        <v>0.61</v>
+      </c>
+      <c r="F56">
+        <v>8.1</v>
+      </c>
+      <c r="G56">
+        <v>8.59</v>
+      </c>
+      <c r="H56">
+        <v>0.27</v>
+      </c>
+      <c r="I56">
+        <v>3.8</v>
+      </c>
+      <c r="J56">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="K56">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="L56">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57" t="s">
+        <v>13</v>
+      </c>
+      <c r="B57" t="s">
+        <v>37</v>
+      </c>
+      <c r="C57">
+        <v>19.72</v>
+      </c>
+      <c r="D57">
+        <v>28.49</v>
+      </c>
+      <c r="E57">
+        <v>-0.05</v>
+      </c>
+      <c r="F57">
+        <v>-0.2</v>
+      </c>
+      <c r="G57">
+        <v>27.07</v>
+      </c>
+      <c r="H57">
+        <v>-1.03</v>
+      </c>
+      <c r="I57">
+        <v>-4.5</v>
+      </c>
+      <c r="J57">
+        <v>25.64</v>
+      </c>
+      <c r="K57">
+        <v>-2.02</v>
+      </c>
+      <c r="L57">
+        <v>-9.4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58" t="s">
+        <v>13</v>
+      </c>
+      <c r="B58" t="s">
+        <v>38</v>
+      </c>
+      <c r="C58">
+        <v>6.26</v>
+      </c>
+      <c r="D58">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="E58">
+        <v>0.61</v>
+      </c>
+      <c r="F58">
+        <v>8.1</v>
+      </c>
+      <c r="G58">
+        <v>8.59</v>
+      </c>
+      <c r="H58">
+        <v>0.27</v>
+      </c>
+      <c r="I58">
+        <v>3.8</v>
+      </c>
+      <c r="J58">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="K58">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="L58">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" t="s">
+        <v>13</v>
+      </c>
+      <c r="B59" t="s">
+        <v>39</v>
+      </c>
+      <c r="C59">
+        <v>19.72</v>
+      </c>
+      <c r="D59">
+        <v>28.49</v>
+      </c>
+      <c r="E59">
+        <v>-0.05</v>
+      </c>
+      <c r="F59">
+        <v>-0.2</v>
+      </c>
+      <c r="G59">
+        <v>27.07</v>
+      </c>
+      <c r="H59">
+        <v>-1.03</v>
+      </c>
+      <c r="I59">
+        <v>-4.5</v>
+      </c>
+      <c r="J59">
+        <v>25.64</v>
+      </c>
+      <c r="K59">
+        <v>-2.02</v>
+      </c>
+      <c r="L59">
+        <v>-9.4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="A60" t="s">
+        <v>13</v>
+      </c>
+      <c r="B60" t="s">
+        <v>40</v>
+      </c>
+      <c r="C60">
+        <v>6.78</v>
+      </c>
+      <c r="D60">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="E60">
+        <v>0.66</v>
+      </c>
+      <c r="F60">
+        <v>8.1</v>
+      </c>
+      <c r="G60">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H60">
+        <v>0.29</v>
+      </c>
+      <c r="I60">
+        <v>3.7</v>
+      </c>
+      <c r="J60">
+        <v>8.81</v>
+      </c>
+      <c r="K60">
+        <v>-0.08</v>
+      </c>
+      <c r="L60">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="A61" t="s">
+        <v>13</v>
+      </c>
+      <c r="B61" t="s">
+        <v>41</v>
+      </c>
+      <c r="C61">
+        <v>2.5</v>
+      </c>
+      <c r="D61">
+        <v>3.61</v>
+      </c>
+      <c r="E61">
+        <v>0.24</v>
+      </c>
+      <c r="F61">
+        <v>8.1</v>
+      </c>
+      <c r="G61">
+        <v>3.43</v>
+      </c>
+      <c r="H61">
+        <v>0.11</v>
+      </c>
+      <c r="I61">
+        <v>3.7</v>
+      </c>
+      <c r="J61">
+        <v>3.25</v>
+      </c>
+      <c r="K61">
+        <v>-0.03</v>
+      </c>
+      <c r="L61">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62" t="s">
+        <v>13</v>
+      </c>
+      <c r="B62" t="s">
+        <v>42</v>
+      </c>
+      <c r="C62">
+        <v>6.55</v>
+      </c>
+      <c r="D62">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="E62">
+        <v>0.65</v>
+      </c>
+      <c r="F62">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G62">
+        <v>9</v>
+      </c>
+      <c r="H62">
+        <v>0.29</v>
+      </c>
+      <c r="I62">
+        <v>3.9</v>
+      </c>
+      <c r="J62">
+        <v>8.52</v>
+      </c>
+      <c r="K62">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="L62">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63" t="s">
+        <v>13</v>
+      </c>
+      <c r="B63" t="s">
+        <v>43</v>
+      </c>
+      <c r="C63">
+        <v>9.92</v>
+      </c>
+      <c r="D63">
+        <v>35.69</v>
+      </c>
+      <c r="E63">
+        <v>14.72</v>
+      </c>
+      <c r="F63">
+        <v>49.1</v>
+      </c>
+      <c r="G63">
+        <v>33.91</v>
+      </c>
+      <c r="H63">
+        <v>13.49</v>
+      </c>
+      <c r="I63">
+        <v>47.3</v>
+      </c>
+      <c r="J63">
+        <v>32.12</v>
+      </c>
+      <c r="K63">
+        <v>12.25</v>
+      </c>
+      <c r="L63">
+        <v>45.4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64" t="s">
+        <v>13</v>
+      </c>
+      <c r="B64" t="s">
+        <v>44</v>
+      </c>
+      <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64">
+        <v>26.17</v>
+      </c>
+      <c r="E64">
+        <v>15.07</v>
+      </c>
+      <c r="F64">
+        <v>68.5</v>
+      </c>
+      <c r="G64">
+        <v>24.86</v>
+      </c>
+      <c r="H64">
+        <v>14.16</v>
+      </c>
+      <c r="I64">
+        <v>67.8</v>
+      </c>
+      <c r="J64">
+        <v>23.55</v>
+      </c>
+      <c r="K64">
+        <v>13.26</v>
+      </c>
+      <c r="L64">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="A65" t="s">
+        <v>13</v>
+      </c>
+      <c r="B65" t="s">
+        <v>45</v>
+      </c>
+      <c r="C65">
+        <v>7.98</v>
+      </c>
+      <c r="D65">
+        <v>33.5</v>
+      </c>
+      <c r="E65">
+        <v>15.15</v>
+      </c>
+      <c r="F65">
+        <v>53.8</v>
+      </c>
+      <c r="G65">
+        <v>31.83</v>
+      </c>
+      <c r="H65">
+        <v>13.99</v>
+      </c>
+      <c r="I65">
+        <v>52.3</v>
+      </c>
+      <c r="J65">
+        <v>30.15</v>
+      </c>
+      <c r="K65">
+        <v>12.83</v>
+      </c>
+      <c r="L65">
+        <v>50.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I129"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>3.87</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>11.99</v>
+      </c>
+      <c r="F2">
+        <v>10.79</v>
+      </c>
+      <c r="G2">
+        <v>48.3</v>
+      </c>
+      <c r="H2">
+        <v>44.6</v>
+      </c>
+      <c r="I2">
+        <v>6.38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <v>3.87</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>11.99</v>
+      </c>
+      <c r="F3">
+        <v>10.79</v>
+      </c>
+      <c r="G3">
+        <v>54.2</v>
+      </c>
+      <c r="H3">
+        <v>51.1</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <v>3.87</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>19.99</v>
+      </c>
+      <c r="F4">
+        <v>17.99</v>
+      </c>
+      <c r="G4">
+        <v>61.8</v>
+      </c>
+      <c r="H4">
+        <v>59.6</v>
+      </c>
+      <c r="I4">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>3.87</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>19.99</v>
+      </c>
+      <c r="F5">
+        <v>17.99</v>
+      </c>
+      <c r="G5">
+        <v>65.3</v>
+      </c>
+      <c r="H5">
+        <v>63.4</v>
+      </c>
+      <c r="I5">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>3.87</v>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>19.99</v>
+      </c>
+      <c r="F6">
+        <v>17.99</v>
+      </c>
+      <c r="G6">
+        <v>61.8</v>
+      </c>
+      <c r="H6">
+        <v>59.6</v>
+      </c>
+      <c r="I6">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>3.87</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>19.99</v>
+      </c>
+      <c r="F7">
+        <v>17.99</v>
+      </c>
+      <c r="G7">
+        <v>65.3</v>
+      </c>
+      <c r="H7">
+        <v>63.4</v>
+      </c>
+      <c r="I7">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8">
+        <v>3.87</v>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>19.99</v>
+      </c>
+      <c r="F8">
+        <v>17.99</v>
+      </c>
+      <c r="G8">
+        <v>61.8</v>
+      </c>
+      <c r="H8">
+        <v>59.6</v>
+      </c>
+      <c r="I8">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <v>3.87</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>19.99</v>
+      </c>
+      <c r="F9">
+        <v>17.99</v>
+      </c>
+      <c r="G9">
+        <v>65.3</v>
+      </c>
+      <c r="H9">
+        <v>63.4</v>
+      </c>
+      <c r="I9">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <v>3.87</v>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>19.99</v>
+      </c>
+      <c r="F10">
+        <v>17.99</v>
+      </c>
+      <c r="G10">
+        <v>61.8</v>
+      </c>
+      <c r="H10">
+        <v>59.6</v>
+      </c>
+      <c r="I10">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11">
+        <v>3.87</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>19.99</v>
+      </c>
+      <c r="F11">
+        <v>17.99</v>
+      </c>
+      <c r="G11">
+        <v>65.3</v>
+      </c>
+      <c r="H11">
+        <v>63.4</v>
+      </c>
+      <c r="I11">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12">
+        <v>3.87</v>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>19.99</v>
+      </c>
+      <c r="F12">
+        <v>17.99</v>
+      </c>
+      <c r="G12">
+        <v>61.8</v>
+      </c>
+      <c r="H12">
+        <v>59.6</v>
+      </c>
+      <c r="I12">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13">
+        <v>3.87</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>19.99</v>
+      </c>
+      <c r="F13">
+        <v>17.99</v>
+      </c>
+      <c r="G13">
+        <v>65.3</v>
+      </c>
+      <c r="H13">
+        <v>63.4</v>
+      </c>
+      <c r="I13">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14">
+        <v>3.87</v>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>19.99</v>
+      </c>
+      <c r="F14">
+        <v>17.99</v>
+      </c>
+      <c r="G14">
+        <v>61.8</v>
+      </c>
+      <c r="H14">
+        <v>59.6</v>
+      </c>
+      <c r="I14">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>3.87</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>19.99</v>
+      </c>
+      <c r="F15">
+        <v>17.99</v>
+      </c>
+      <c r="G15">
+        <v>65.3</v>
+      </c>
+      <c r="H15">
+        <v>63.4</v>
+      </c>
+      <c r="I15">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16">
+        <v>3.87</v>
+      </c>
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>11.99</v>
+      </c>
+      <c r="F16">
+        <v>10.79</v>
+      </c>
+      <c r="G16">
+        <v>48.3</v>
+      </c>
+      <c r="H16">
+        <v>44.6</v>
+      </c>
+      <c r="I16">
+        <v>6.38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17">
+        <v>3.87</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>11.99</v>
+      </c>
+      <c r="F17">
+        <v>10.79</v>
+      </c>
+      <c r="G17">
+        <v>54.2</v>
+      </c>
+      <c r="H17">
+        <v>51.1</v>
+      </c>
+      <c r="I17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18">
+        <v>14.76</v>
+      </c>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>54.99</v>
+      </c>
+      <c r="F18">
+        <v>49.49</v>
+      </c>
+      <c r="G18">
+        <v>54</v>
+      </c>
+      <c r="H18">
+        <v>50.9</v>
+      </c>
+      <c r="I18">
+        <v>27.61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19">
+        <v>14.76</v>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>54.99</v>
+      </c>
+      <c r="F19">
+        <v>49.49</v>
+      </c>
+      <c r="G19">
+        <v>58.9</v>
+      </c>
+      <c r="H19">
+        <v>56.3</v>
+      </c>
+      <c r="I19">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20">
+        <v>14.62</v>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>52.99</v>
+      </c>
+      <c r="F20">
+        <v>47.69</v>
+      </c>
+      <c r="G20">
+        <v>53.2</v>
+      </c>
+      <c r="H20">
+        <v>50</v>
+      </c>
+      <c r="I20">
+        <v>27.34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21">
+        <v>14.62</v>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>52.99</v>
+      </c>
+      <c r="F21">
+        <v>47.69</v>
+      </c>
+      <c r="G21">
+        <v>58.2</v>
+      </c>
+      <c r="H21">
+        <v>55.6</v>
+      </c>
+      <c r="I21">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22">
+        <v>14.68</v>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>52.99</v>
+      </c>
+      <c r="F22">
+        <v>47.69</v>
+      </c>
+      <c r="G22">
+        <v>53.1</v>
+      </c>
+      <c r="H22">
+        <v>49.9</v>
+      </c>
+      <c r="I22">
+        <v>27.45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23">
+        <v>14.68</v>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>52.99</v>
+      </c>
+      <c r="F23">
+        <v>47.69</v>
+      </c>
+      <c r="G23">
+        <v>58.1</v>
+      </c>
+      <c r="H23">
+        <v>55.5</v>
+      </c>
+      <c r="I23">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24">
+        <v>7.81</v>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>24.99</v>
+      </c>
+      <c r="F24">
+        <v>22.49</v>
+      </c>
+      <c r="G24">
+        <v>49.4</v>
+      </c>
+      <c r="H24">
+        <v>45.8</v>
+      </c>
+      <c r="I24">
+        <v>14.61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25">
+        <v>7.81</v>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>24.99</v>
+      </c>
+      <c r="F25">
+        <v>22.49</v>
+      </c>
+      <c r="G25">
+        <v>55</v>
+      </c>
+      <c r="H25">
+        <v>52.1</v>
+      </c>
+      <c r="I25">
+        <v>12.49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26">
+        <v>7.81</v>
+      </c>
+      <c r="D26" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>27.99</v>
+      </c>
+      <c r="F26">
+        <v>25.19</v>
+      </c>
+      <c r="G26">
+        <v>52.9</v>
+      </c>
+      <c r="H26">
+        <v>49.6</v>
+      </c>
+      <c r="I26">
+        <v>14.61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27">
+        <v>7.81</v>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>27.99</v>
+      </c>
+      <c r="F27">
+        <v>25.19</v>
+      </c>
+      <c r="G27">
+        <v>57.9</v>
+      </c>
+      <c r="H27">
+        <v>55.3</v>
+      </c>
+      <c r="I27">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28">
+        <v>3.03</v>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>3.68</v>
+      </c>
+      <c r="F28">
+        <v>3.31</v>
+      </c>
+      <c r="G28">
+        <v>4.5</v>
+      </c>
+      <c r="H28">
+        <v>-5.1</v>
+      </c>
+      <c r="I28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29">
+        <v>3.03</v>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>3.68</v>
+      </c>
+      <c r="F29">
+        <v>3.31</v>
+      </c>
+      <c r="G29">
+        <v>19.4</v>
+      </c>
+      <c r="H29">
+        <v>11.5</v>
+      </c>
+      <c r="I29">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30">
+        <v>11.07</v>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>35.99</v>
+      </c>
+      <c r="F30">
+        <v>32.39</v>
+      </c>
+      <c r="G30">
+        <v>49.9</v>
+      </c>
+      <c r="H30">
+        <v>46.3</v>
+      </c>
+      <c r="I30">
+        <v>20.71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31">
+        <v>11.07</v>
+      </c>
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>35.99</v>
+      </c>
+      <c r="F31">
+        <v>32.39</v>
+      </c>
+      <c r="G31">
+        <v>55.5</v>
+      </c>
+      <c r="H31">
+        <v>52.5</v>
+      </c>
+      <c r="I31">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32">
+        <v>11.07</v>
+      </c>
+      <c r="D32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>35.99</v>
+      </c>
+      <c r="F32">
+        <v>32.39</v>
+      </c>
+      <c r="G32">
+        <v>49.9</v>
+      </c>
+      <c r="H32">
+        <v>46.3</v>
+      </c>
+      <c r="I32">
+        <v>20.71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33">
+        <v>11.07</v>
+      </c>
+      <c r="D33" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>35.99</v>
+      </c>
+      <c r="F33">
+        <v>32.39</v>
+      </c>
+      <c r="G33">
+        <v>55.5</v>
+      </c>
+      <c r="H33">
+        <v>52.5</v>
+      </c>
+      <c r="I33">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34">
+        <v>7.63</v>
+      </c>
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>25.99</v>
+      </c>
+      <c r="F34">
+        <v>23.39</v>
+      </c>
+      <c r="G34">
+        <v>51.4</v>
+      </c>
+      <c r="H34">
+        <v>48</v>
+      </c>
+      <c r="I34">
+        <v>14.28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35">
+        <v>7.63</v>
+      </c>
+      <c r="D35" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>25.99</v>
+      </c>
+      <c r="F35">
+        <v>23.39</v>
+      </c>
+      <c r="G35">
+        <v>56.7</v>
+      </c>
+      <c r="H35">
+        <v>53.9</v>
+      </c>
+      <c r="I35">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="D36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>27.99</v>
+      </c>
+      <c r="F36">
+        <v>25.19</v>
+      </c>
+      <c r="G36">
+        <v>48.9</v>
+      </c>
+      <c r="H36">
+        <v>45.2</v>
+      </c>
+      <c r="I36">
+        <v>16.61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="D37" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>27.99</v>
+      </c>
+      <c r="F37">
+        <v>25.19</v>
+      </c>
+      <c r="G37">
+        <v>54.6</v>
+      </c>
+      <c r="H37">
+        <v>51.6</v>
+      </c>
+      <c r="I37">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38">
+        <v>12.1</v>
+      </c>
+      <c r="D38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>45.99</v>
+      </c>
+      <c r="F38">
+        <v>41.39</v>
+      </c>
+      <c r="G38">
+        <v>54.5</v>
+      </c>
+      <c r="H38">
+        <v>51.5</v>
+      </c>
+      <c r="I38">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39">
+        <v>12.1</v>
+      </c>
+      <c r="D39" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>45.99</v>
+      </c>
+      <c r="F39">
+        <v>41.39</v>
+      </c>
+      <c r="G39">
+        <v>59.3</v>
+      </c>
+      <c r="H39">
+        <v>56.8</v>
+      </c>
+      <c r="I39">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="D40" t="b">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>27.99</v>
+      </c>
+      <c r="F40">
+        <v>25.19</v>
+      </c>
+      <c r="G40">
+        <v>48.9</v>
+      </c>
+      <c r="H40">
+        <v>45.2</v>
+      </c>
+      <c r="I40">
+        <v>16.61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" t="s">
+        <v>33</v>
+      </c>
+      <c r="C41">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="D41" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41">
+        <v>27.99</v>
+      </c>
+      <c r="F41">
+        <v>25.19</v>
+      </c>
+      <c r="G41">
+        <v>54.6</v>
+      </c>
+      <c r="H41">
+        <v>51.6</v>
+      </c>
+      <c r="I41">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" t="s">
+        <v>34</v>
+      </c>
+      <c r="C42">
+        <v>8.85</v>
+      </c>
+      <c r="D42" t="b">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>29.99</v>
+      </c>
+      <c r="F42">
+        <v>26.99</v>
+      </c>
+      <c r="G42">
+        <v>51.2</v>
+      </c>
+      <c r="H42">
+        <v>47.8</v>
+      </c>
+      <c r="I42">
+        <v>16.55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43">
+        <v>8.85</v>
+      </c>
+      <c r="D43" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>29.99</v>
+      </c>
+      <c r="F43">
+        <v>26.99</v>
+      </c>
+      <c r="G43">
+        <v>56.6</v>
+      </c>
+      <c r="H43">
+        <v>53.7</v>
+      </c>
+      <c r="I43">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" t="s">
+        <v>35</v>
+      </c>
+      <c r="C44">
+        <v>6.91</v>
+      </c>
+      <c r="D44" t="b">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>29.99</v>
+      </c>
+      <c r="F44">
+        <v>26.99</v>
+      </c>
+      <c r="G44">
+        <v>58</v>
+      </c>
+      <c r="H44">
+        <v>55.3</v>
+      </c>
+      <c r="I44">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45" t="s">
+        <v>35</v>
+      </c>
+      <c r="C45">
+        <v>6.91</v>
+      </c>
+      <c r="D45" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>29.99</v>
+      </c>
+      <c r="F45">
+        <v>26.99</v>
+      </c>
+      <c r="G45">
+        <v>62.1</v>
+      </c>
+      <c r="H45">
+        <v>59.9</v>
+      </c>
+      <c r="I45">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" t="s">
+        <v>36</v>
+      </c>
+      <c r="C46">
+        <v>6.26</v>
+      </c>
+      <c r="D46" t="b">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>7.6</v>
+      </c>
+      <c r="F46">
+        <v>6.84</v>
+      </c>
+      <c r="G46">
+        <v>4.5</v>
+      </c>
+      <c r="H46">
+        <v>-5.1</v>
+      </c>
+      <c r="I46">
+        <v>11.71</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" t="s">
+        <v>36</v>
+      </c>
+      <c r="C47">
+        <v>6.26</v>
+      </c>
+      <c r="D47" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47">
+        <v>7.6</v>
+      </c>
+      <c r="F47">
+        <v>6.84</v>
+      </c>
+      <c r="G47">
+        <v>19.4</v>
+      </c>
+      <c r="H47">
+        <v>11.5</v>
+      </c>
+      <c r="I47">
+        <v>8.52</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" t="s">
+        <v>37</v>
+      </c>
+      <c r="C48">
+        <v>19.72</v>
+      </c>
+      <c r="D48" t="b">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>23.92</v>
+      </c>
+      <c r="F48">
+        <v>21.53</v>
+      </c>
+      <c r="G48">
+        <v>-4</v>
+      </c>
+      <c r="H48">
+        <v>-13.6</v>
+      </c>
+      <c r="I48">
+        <v>36.88</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" t="s">
+        <v>12</v>
+      </c>
+      <c r="B49" t="s">
+        <v>37</v>
+      </c>
+      <c r="C49">
+        <v>19.72</v>
+      </c>
+      <c r="D49" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49">
+        <v>23.92</v>
+      </c>
+      <c r="F49">
+        <v>21.53</v>
+      </c>
+      <c r="G49">
+        <v>10.9</v>
+      </c>
+      <c r="H49">
+        <v>3</v>
+      </c>
+      <c r="I49">
+        <v>30.48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" t="s">
+        <v>38</v>
+      </c>
+      <c r="C50">
+        <v>6.26</v>
+      </c>
+      <c r="D50" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>7.6</v>
+      </c>
+      <c r="F50">
+        <v>6.84</v>
+      </c>
+      <c r="G50">
+        <v>4.5</v>
+      </c>
+      <c r="H50">
+        <v>-5.1</v>
+      </c>
+      <c r="I50">
+        <v>11.71</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" t="s">
+        <v>38</v>
+      </c>
+      <c r="C51">
+        <v>6.26</v>
+      </c>
+      <c r="D51" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51">
+        <v>7.6</v>
+      </c>
+      <c r="F51">
+        <v>6.84</v>
+      </c>
+      <c r="G51">
+        <v>19.4</v>
+      </c>
+      <c r="H51">
+        <v>11.5</v>
+      </c>
+      <c r="I51">
+        <v>8.52</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" t="s">
+        <v>39</v>
+      </c>
+      <c r="C52">
+        <v>19.72</v>
+      </c>
+      <c r="D52" t="b">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>23.92</v>
+      </c>
+      <c r="F52">
+        <v>21.53</v>
+      </c>
+      <c r="G52">
+        <v>-4</v>
+      </c>
+      <c r="H52">
+        <v>-13.6</v>
+      </c>
+      <c r="I52">
+        <v>36.88</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" t="s">
+        <v>39</v>
+      </c>
+      <c r="C53">
+        <v>19.72</v>
+      </c>
+      <c r="D53" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53">
+        <v>23.92</v>
+      </c>
+      <c r="F53">
+        <v>21.53</v>
+      </c>
+      <c r="G53">
+        <v>10.9</v>
+      </c>
+      <c r="H53">
+        <v>3</v>
+      </c>
+      <c r="I53">
+        <v>30.48</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54" t="s">
+        <v>40</v>
+      </c>
+      <c r="C54">
+        <v>6.78</v>
+      </c>
+      <c r="D54" t="b">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="F54">
+        <v>7.4</v>
+      </c>
+      <c r="G54">
+        <v>4.3</v>
+      </c>
+      <c r="H54">
+        <v>-5.2</v>
+      </c>
+      <c r="I54">
+        <v>12.69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" t="s">
+        <v>40</v>
+      </c>
+      <c r="C55">
+        <v>6.78</v>
+      </c>
+      <c r="D55" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="F55">
+        <v>7.4</v>
+      </c>
+      <c r="G55">
+        <v>19.3</v>
+      </c>
+      <c r="H55">
+        <v>11.4</v>
+      </c>
+      <c r="I55">
+        <v>9.23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" t="s">
+        <v>41</v>
+      </c>
+      <c r="C56">
+        <v>2.5</v>
+      </c>
+      <c r="D56" t="b">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>3.03</v>
+      </c>
+      <c r="F56">
+        <v>2.73</v>
+      </c>
+      <c r="G56">
+        <v>4.3</v>
+      </c>
+      <c r="H56">
+        <v>-5.2</v>
+      </c>
+      <c r="I56">
+        <v>4.12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57" t="s">
+        <v>41</v>
+      </c>
+      <c r="C57">
+        <v>2.5</v>
+      </c>
+      <c r="D57" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57">
+        <v>3.03</v>
+      </c>
+      <c r="F57">
+        <v>2.73</v>
+      </c>
+      <c r="G57">
+        <v>19.2</v>
+      </c>
+      <c r="H57">
+        <v>11.4</v>
+      </c>
+      <c r="I57">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" t="s">
+        <v>12</v>
+      </c>
+      <c r="B58" t="s">
+        <v>42</v>
+      </c>
+      <c r="C58">
+        <v>6.55</v>
+      </c>
+      <c r="D58" t="b">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>7.94</v>
+      </c>
+      <c r="F58">
+        <v>7.15</v>
+      </c>
+      <c r="G58">
+        <v>4.3</v>
+      </c>
+      <c r="H58">
+        <v>-5.2</v>
+      </c>
+      <c r="I58">
+        <v>12.25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" t="s">
+        <v>12</v>
+      </c>
+      <c r="B59" t="s">
+        <v>42</v>
+      </c>
+      <c r="C59">
+        <v>6.55</v>
+      </c>
+      <c r="D59" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59">
+        <v>7.94</v>
+      </c>
+      <c r="F59">
+        <v>7.15</v>
+      </c>
+      <c r="G59">
+        <v>19.3</v>
+      </c>
+      <c r="H59">
+        <v>11.4</v>
+      </c>
+      <c r="I59">
+        <v>8.92</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" t="s">
+        <v>12</v>
+      </c>
+      <c r="B60" t="s">
+        <v>43</v>
+      </c>
+      <c r="C60">
+        <v>9.92</v>
+      </c>
+      <c r="D60" t="b">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>29.99</v>
+      </c>
+      <c r="F60">
+        <v>26.99</v>
+      </c>
+      <c r="G60">
+        <v>47.5</v>
+      </c>
+      <c r="H60">
+        <v>43.6</v>
+      </c>
+      <c r="I60">
+        <v>18.55</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" t="s">
+        <v>12</v>
+      </c>
+      <c r="B61" t="s">
+        <v>43</v>
+      </c>
+      <c r="C61">
+        <v>9.92</v>
+      </c>
+      <c r="D61" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61">
+        <v>29.99</v>
+      </c>
+      <c r="F61">
+        <v>26.99</v>
+      </c>
+      <c r="G61">
+        <v>53.5</v>
+      </c>
+      <c r="H61">
+        <v>50.3</v>
+      </c>
+      <c r="I61">
+        <v>15.33</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62" t="s">
+        <v>44</v>
+      </c>
+      <c r="C62">
+        <v>3</v>
+      </c>
+      <c r="D62" t="b">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>21.99</v>
+      </c>
+      <c r="F62">
+        <v>19.79</v>
+      </c>
+      <c r="G62">
+        <v>67.8</v>
+      </c>
+      <c r="H62">
+        <v>66.2</v>
+      </c>
+      <c r="I62">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" t="s">
+        <v>12</v>
+      </c>
+      <c r="B63" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63">
+        <v>3</v>
+      </c>
+      <c r="D63" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63">
+        <v>21.99</v>
+      </c>
+      <c r="F63">
+        <v>19.79</v>
+      </c>
+      <c r="G63">
+        <v>70.2</v>
+      </c>
+      <c r="H63">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="I63">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" t="s">
+        <v>12</v>
+      </c>
+      <c r="B64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C64">
+        <v>7.98</v>
+      </c>
+      <c r="D64" t="b">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>28.99</v>
+      </c>
+      <c r="F64">
+        <v>26.09</v>
+      </c>
+      <c r="G64">
+        <v>53.3</v>
+      </c>
+      <c r="H64">
+        <v>50.1</v>
+      </c>
+      <c r="I64">
+        <v>14.93</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" t="s">
+        <v>45</v>
+      </c>
+      <c r="C65">
+        <v>7.98</v>
+      </c>
+      <c r="D65" t="b">
+        <v>1</v>
+      </c>
+      <c r="E65">
+        <v>28.99</v>
+      </c>
+      <c r="F65">
+        <v>26.09</v>
+      </c>
+      <c r="G65">
+        <v>58.3</v>
+      </c>
+      <c r="H65">
+        <v>55.6</v>
+      </c>
+      <c r="I65">
+        <v>14.49</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B66" t="s">
+        <v>14</v>
+      </c>
+      <c r="C66">
+        <v>3.87</v>
+      </c>
+      <c r="D66" t="b">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>14.27</v>
+      </c>
+      <c r="F66">
+        <v>12.84</v>
+      </c>
+      <c r="G66">
+        <v>49.9</v>
+      </c>
+      <c r="H66">
+        <v>46.3</v>
+      </c>
+      <c r="I66">
+        <v>7.27</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" t="s">
+        <v>13</v>
+      </c>
+      <c r="B67" t="s">
+        <v>14</v>
+      </c>
+      <c r="C67">
+        <v>3.87</v>
+      </c>
+      <c r="D67" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67">
+        <v>14.27</v>
+      </c>
+      <c r="F67">
+        <v>12.84</v>
+      </c>
+      <c r="G67">
+        <v>55.5</v>
+      </c>
+      <c r="H67">
+        <v>52.5</v>
+      </c>
+      <c r="I67">
+        <v>7.13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" t="s">
+        <v>13</v>
+      </c>
+      <c r="B68" t="s">
+        <v>15</v>
+      </c>
+      <c r="C68">
+        <v>3.87</v>
+      </c>
+      <c r="D68" t="b">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>23.79</v>
+      </c>
+      <c r="F68">
+        <v>21.41</v>
+      </c>
+      <c r="G68">
+        <v>62.8</v>
+      </c>
+      <c r="H68">
+        <v>60.6</v>
+      </c>
+      <c r="I68">
+        <v>11.89</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" t="s">
+        <v>13</v>
+      </c>
+      <c r="B69" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69">
+        <v>3.87</v>
+      </c>
+      <c r="D69" t="b">
+        <v>1</v>
+      </c>
+      <c r="E69">
+        <v>23.79</v>
+      </c>
+      <c r="F69">
+        <v>21.41</v>
+      </c>
+      <c r="G69">
+        <v>66.2</v>
+      </c>
+      <c r="H69">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="I69">
+        <v>11.89</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" t="s">
+        <v>13</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70">
+        <v>3.87</v>
+      </c>
+      <c r="D70" t="b">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>23.79</v>
+      </c>
+      <c r="F70">
+        <v>21.41</v>
+      </c>
+      <c r="G70">
+        <v>62.8</v>
+      </c>
+      <c r="H70">
+        <v>60.6</v>
+      </c>
+      <c r="I70">
+        <v>11.89</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" t="s">
+        <v>13</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71">
+        <v>3.87</v>
+      </c>
+      <c r="D71" t="b">
+        <v>1</v>
+      </c>
+      <c r="E71">
+        <v>23.79</v>
+      </c>
+      <c r="F71">
+        <v>21.41</v>
+      </c>
+      <c r="G71">
+        <v>66.2</v>
+      </c>
+      <c r="H71">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="I71">
+        <v>11.89</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" t="s">
+        <v>13</v>
+      </c>
+      <c r="B72" t="s">
+        <v>17</v>
+      </c>
+      <c r="C72">
+        <v>3.87</v>
+      </c>
+      <c r="D72" t="b">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>23.79</v>
+      </c>
+      <c r="F72">
+        <v>21.41</v>
+      </c>
+      <c r="G72">
+        <v>62.8</v>
+      </c>
+      <c r="H72">
+        <v>60.6</v>
+      </c>
+      <c r="I72">
+        <v>11.89</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" t="s">
+        <v>13</v>
+      </c>
+      <c r="B73" t="s">
+        <v>17</v>
+      </c>
+      <c r="C73">
+        <v>3.87</v>
+      </c>
+      <c r="D73" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73">
+        <v>23.79</v>
+      </c>
+      <c r="F73">
+        <v>21.41</v>
+      </c>
+      <c r="G73">
+        <v>66.2</v>
+      </c>
+      <c r="H73">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="I73">
+        <v>11.89</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" t="s">
+        <v>13</v>
+      </c>
+      <c r="B74" t="s">
+        <v>18</v>
+      </c>
+      <c r="C74">
+        <v>3.87</v>
+      </c>
+      <c r="D74" t="b">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>23.79</v>
+      </c>
+      <c r="F74">
+        <v>21.41</v>
+      </c>
+      <c r="G74">
+        <v>62.8</v>
+      </c>
+      <c r="H74">
+        <v>60.6</v>
+      </c>
+      <c r="I74">
+        <v>11.89</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" t="s">
+        <v>13</v>
+      </c>
+      <c r="B75" t="s">
+        <v>18</v>
+      </c>
+      <c r="C75">
+        <v>3.87</v>
+      </c>
+      <c r="D75" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75">
+        <v>23.79</v>
+      </c>
+      <c r="F75">
+        <v>21.41</v>
+      </c>
+      <c r="G75">
+        <v>66.2</v>
+      </c>
+      <c r="H75">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="I75">
+        <v>11.89</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" t="s">
+        <v>13</v>
+      </c>
+      <c r="B76" t="s">
+        <v>19</v>
+      </c>
+      <c r="C76">
+        <v>3.87</v>
+      </c>
+      <c r="D76" t="b">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>23.79</v>
+      </c>
+      <c r="F76">
+        <v>21.41</v>
+      </c>
+      <c r="G76">
+        <v>62.8</v>
+      </c>
+      <c r="H76">
+        <v>60.6</v>
+      </c>
+      <c r="I76">
+        <v>11.89</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" t="s">
+        <v>13</v>
+      </c>
+      <c r="B77" t="s">
+        <v>19</v>
+      </c>
+      <c r="C77">
+        <v>3.87</v>
+      </c>
+      <c r="D77" t="b">
+        <v>1</v>
+      </c>
+      <c r="E77">
+        <v>23.79</v>
+      </c>
+      <c r="F77">
+        <v>21.41</v>
+      </c>
+      <c r="G77">
+        <v>66.2</v>
+      </c>
+      <c r="H77">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="I77">
+        <v>11.89</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" t="s">
+        <v>13</v>
+      </c>
+      <c r="B78" t="s">
+        <v>20</v>
+      </c>
+      <c r="C78">
+        <v>3.87</v>
+      </c>
+      <c r="D78" t="b">
+        <v>0</v>
+      </c>
+      <c r="E78">
+        <v>23.79</v>
+      </c>
+      <c r="F78">
+        <v>21.41</v>
+      </c>
+      <c r="G78">
+        <v>62.8</v>
+      </c>
+      <c r="H78">
+        <v>60.6</v>
+      </c>
+      <c r="I78">
+        <v>11.89</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" t="s">
+        <v>13</v>
+      </c>
+      <c r="B79" t="s">
+        <v>20</v>
+      </c>
+      <c r="C79">
+        <v>3.87</v>
+      </c>
+      <c r="D79" t="b">
+        <v>1</v>
+      </c>
+      <c r="E79">
+        <v>23.79</v>
+      </c>
+      <c r="F79">
+        <v>21.41</v>
+      </c>
+      <c r="G79">
+        <v>66.2</v>
+      </c>
+      <c r="H79">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="I79">
+        <v>11.89</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" t="s">
+        <v>13</v>
+      </c>
+      <c r="B80" t="s">
+        <v>21</v>
+      </c>
+      <c r="C80">
+        <v>3.87</v>
+      </c>
+      <c r="D80" t="b">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>14.27</v>
+      </c>
+      <c r="F80">
+        <v>12.84</v>
+      </c>
+      <c r="G80">
+        <v>49.9</v>
+      </c>
+      <c r="H80">
+        <v>46.3</v>
+      </c>
+      <c r="I80">
+        <v>7.27</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" t="s">
+        <v>13</v>
+      </c>
+      <c r="B81" t="s">
+        <v>21</v>
+      </c>
+      <c r="C81">
+        <v>3.87</v>
+      </c>
+      <c r="D81" t="b">
+        <v>1</v>
+      </c>
+      <c r="E81">
+        <v>14.27</v>
+      </c>
+      <c r="F81">
+        <v>12.84</v>
+      </c>
+      <c r="G81">
+        <v>55.5</v>
+      </c>
+      <c r="H81">
+        <v>52.5</v>
+      </c>
+      <c r="I81">
+        <v>7.13</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" t="s">
+        <v>13</v>
+      </c>
+      <c r="B82" t="s">
+        <v>22</v>
+      </c>
+      <c r="C82">
+        <v>14.76</v>
+      </c>
+      <c r="D82" t="b">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>63.55</v>
+      </c>
+      <c r="F82">
+        <v>57.2</v>
+      </c>
+      <c r="G82">
+        <v>54.5</v>
+      </c>
+      <c r="H82">
+        <v>51.4</v>
+      </c>
+      <c r="I82">
+        <v>31.77</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" t="s">
+        <v>13</v>
+      </c>
+      <c r="B83" t="s">
+        <v>22</v>
+      </c>
+      <c r="C83">
+        <v>14.76</v>
+      </c>
+      <c r="D83" t="b">
+        <v>1</v>
+      </c>
+      <c r="E83">
+        <v>63.55</v>
+      </c>
+      <c r="F83">
+        <v>57.2</v>
+      </c>
+      <c r="G83">
+        <v>59.3</v>
+      </c>
+      <c r="H83">
+        <v>56.8</v>
+      </c>
+      <c r="I83">
+        <v>31.77</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" t="s">
+        <v>13</v>
+      </c>
+      <c r="B84" t="s">
+        <v>23</v>
+      </c>
+      <c r="C84">
+        <v>14.62</v>
+      </c>
+      <c r="D84" t="b">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>61.24</v>
+      </c>
+      <c r="F84">
+        <v>55.12</v>
+      </c>
+      <c r="G84">
+        <v>53.7</v>
+      </c>
+      <c r="H84">
+        <v>50.6</v>
+      </c>
+      <c r="I84">
+        <v>31.11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" t="s">
+        <v>13</v>
+      </c>
+      <c r="B85" t="s">
+        <v>23</v>
+      </c>
+      <c r="C85">
+        <v>14.62</v>
+      </c>
+      <c r="D85" t="b">
+        <v>1</v>
+      </c>
+      <c r="E85">
+        <v>61.24</v>
+      </c>
+      <c r="F85">
+        <v>55.12</v>
+      </c>
+      <c r="G85">
+        <v>58.7</v>
+      </c>
+      <c r="H85">
+        <v>56.1</v>
+      </c>
+      <c r="I85">
+        <v>30.62</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" t="s">
+        <v>13</v>
+      </c>
+      <c r="B86" t="s">
+        <v>24</v>
+      </c>
+      <c r="C86">
+        <v>14.68</v>
+      </c>
+      <c r="D86" t="b">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>61.24</v>
+      </c>
+      <c r="F86">
+        <v>55.12</v>
+      </c>
+      <c r="G86">
+        <v>53.6</v>
+      </c>
+      <c r="H86">
+        <v>50.5</v>
+      </c>
+      <c r="I86">
+        <v>31.23</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" t="s">
+        <v>13</v>
+      </c>
+      <c r="B87" t="s">
+        <v>24</v>
+      </c>
+      <c r="C87">
+        <v>14.68</v>
+      </c>
+      <c r="D87" t="b">
+        <v>1</v>
+      </c>
+      <c r="E87">
+        <v>61.24</v>
+      </c>
+      <c r="F87">
+        <v>55.12</v>
+      </c>
+      <c r="G87">
+        <v>58.6</v>
+      </c>
+      <c r="H87">
+        <v>56</v>
+      </c>
+      <c r="I87">
+        <v>30.62</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" t="s">
+        <v>13</v>
+      </c>
+      <c r="B88" t="s">
+        <v>25</v>
+      </c>
+      <c r="C88">
+        <v>7.81</v>
+      </c>
+      <c r="D88" t="b">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>29.74</v>
+      </c>
+      <c r="F88">
+        <v>26.77</v>
+      </c>
+      <c r="G88">
+        <v>50.9</v>
+      </c>
+      <c r="H88">
+        <v>47.4</v>
+      </c>
+      <c r="I88">
+        <v>16.62</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" t="s">
+        <v>13</v>
+      </c>
+      <c r="B89" t="s">
+        <v>25</v>
+      </c>
+      <c r="C89">
+        <v>7.81</v>
+      </c>
+      <c r="D89" t="b">
+        <v>1</v>
+      </c>
+      <c r="E89">
+        <v>29.74</v>
+      </c>
+      <c r="F89">
+        <v>26.77</v>
+      </c>
+      <c r="G89">
+        <v>56.3</v>
+      </c>
+      <c r="H89">
+        <v>53.5</v>
+      </c>
+      <c r="I89">
+        <v>14.87</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" t="s">
+        <v>13</v>
+      </c>
+      <c r="B90" t="s">
+        <v>26</v>
+      </c>
+      <c r="C90">
+        <v>7.81</v>
+      </c>
+      <c r="D90" t="b">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>33.31</v>
+      </c>
+      <c r="F90">
+        <v>29.98</v>
+      </c>
+      <c r="G90">
+        <v>54.2</v>
+      </c>
+      <c r="H90">
+        <v>51.1</v>
+      </c>
+      <c r="I90">
+        <v>16.66</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" t="s">
+        <v>13</v>
+      </c>
+      <c r="B91" t="s">
+        <v>26</v>
+      </c>
+      <c r="C91">
+        <v>7.81</v>
+      </c>
+      <c r="D91" t="b">
+        <v>1</v>
+      </c>
+      <c r="E91">
+        <v>33.31</v>
+      </c>
+      <c r="F91">
+        <v>29.98</v>
+      </c>
+      <c r="G91">
+        <v>59.1</v>
+      </c>
+      <c r="H91">
+        <v>56.5</v>
+      </c>
+      <c r="I91">
+        <v>16.66</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
+      <c r="A92" t="s">
+        <v>13</v>
+      </c>
+      <c r="B92" t="s">
+        <v>27</v>
+      </c>
+      <c r="C92">
+        <v>3.03</v>
+      </c>
+      <c r="D92" t="b">
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>4.38</v>
+      </c>
+      <c r="F92">
+        <v>3.94</v>
+      </c>
+      <c r="G92">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H92">
+        <v>-1</v>
+      </c>
+      <c r="I92">
+        <v>5.69</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" t="s">
+        <v>13</v>
+      </c>
+      <c r="B93" t="s">
+        <v>27</v>
+      </c>
+      <c r="C93">
+        <v>3.03</v>
+      </c>
+      <c r="D93" t="b">
+        <v>1</v>
+      </c>
+      <c r="E93">
+        <v>4.38</v>
+      </c>
+      <c r="F93">
+        <v>3.94</v>
+      </c>
+      <c r="G93">
+        <v>22.4</v>
+      </c>
+      <c r="H93">
+        <v>14.8</v>
+      </c>
+      <c r="I93">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" t="s">
+        <v>13</v>
+      </c>
+      <c r="B94" t="s">
+        <v>28</v>
+      </c>
+      <c r="C94">
+        <v>11.07</v>
+      </c>
+      <c r="D94" t="b">
+        <v>0</v>
+      </c>
+      <c r="E94">
+        <v>42.83</v>
+      </c>
+      <c r="F94">
+        <v>38.55</v>
+      </c>
+      <c r="G94">
+        <v>51.4</v>
+      </c>
+      <c r="H94">
+        <v>48</v>
+      </c>
+      <c r="I94">
+        <v>23.55</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" t="s">
+        <v>13</v>
+      </c>
+      <c r="B95" t="s">
+        <v>28</v>
+      </c>
+      <c r="C95">
+        <v>11.07</v>
+      </c>
+      <c r="D95" t="b">
+        <v>1</v>
+      </c>
+      <c r="E95">
+        <v>42.83</v>
+      </c>
+      <c r="F95">
+        <v>38.55</v>
+      </c>
+      <c r="G95">
+        <v>56.7</v>
+      </c>
+      <c r="H95">
+        <v>53.9</v>
+      </c>
+      <c r="I95">
+        <v>21.41</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" t="s">
+        <v>13</v>
+      </c>
+      <c r="B96" t="s">
+        <v>29</v>
+      </c>
+      <c r="C96">
+        <v>11.07</v>
+      </c>
+      <c r="D96" t="b">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>42.83</v>
+      </c>
+      <c r="F96">
+        <v>38.55</v>
+      </c>
+      <c r="G96">
+        <v>51.4</v>
+      </c>
+      <c r="H96">
+        <v>48</v>
+      </c>
+      <c r="I96">
+        <v>23.55</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" t="s">
+        <v>13</v>
+      </c>
+      <c r="B97" t="s">
+        <v>29</v>
+      </c>
+      <c r="C97">
+        <v>11.07</v>
+      </c>
+      <c r="D97" t="b">
+        <v>1</v>
+      </c>
+      <c r="E97">
+        <v>42.83</v>
+      </c>
+      <c r="F97">
+        <v>38.55</v>
+      </c>
+      <c r="G97">
+        <v>56.7</v>
+      </c>
+      <c r="H97">
+        <v>53.9</v>
+      </c>
+      <c r="I97">
+        <v>21.41</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" t="s">
+        <v>13</v>
+      </c>
+      <c r="B98" t="s">
+        <v>30</v>
+      </c>
+      <c r="C98">
+        <v>7.63</v>
+      </c>
+      <c r="D98" t="b">
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>30.93</v>
+      </c>
+      <c r="F98">
+        <v>27.84</v>
+      </c>
+      <c r="G98">
+        <v>52.8</v>
+      </c>
+      <c r="H98">
+        <v>49.5</v>
+      </c>
+      <c r="I98">
+        <v>16.23</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" t="s">
+        <v>13</v>
+      </c>
+      <c r="B99" t="s">
+        <v>30</v>
+      </c>
+      <c r="C99">
+        <v>7.63</v>
+      </c>
+      <c r="D99" t="b">
+        <v>1</v>
+      </c>
+      <c r="E99">
+        <v>30.93</v>
+      </c>
+      <c r="F99">
+        <v>27.84</v>
+      </c>
+      <c r="G99">
+        <v>57.9</v>
+      </c>
+      <c r="H99">
+        <v>55.2</v>
+      </c>
+      <c r="I99">
+        <v>15.46</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" t="s">
+        <v>13</v>
+      </c>
+      <c r="B100" t="s">
+        <v>31</v>
+      </c>
+      <c r="C100">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="D100" t="b">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>37.88</v>
+      </c>
+      <c r="F100">
+        <v>34.09</v>
+      </c>
+      <c r="G100">
+        <v>54.3</v>
+      </c>
+      <c r="H100">
+        <v>51.2</v>
+      </c>
+      <c r="I100">
+        <v>18.94</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" t="s">
+        <v>13</v>
+      </c>
+      <c r="B101" t="s">
+        <v>31</v>
+      </c>
+      <c r="C101">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="D101" t="b">
+        <v>1</v>
+      </c>
+      <c r="E101">
+        <v>37.88</v>
+      </c>
+      <c r="F101">
+        <v>34.09</v>
+      </c>
+      <c r="G101">
+        <v>59.1</v>
+      </c>
+      <c r="H101">
+        <v>56.5</v>
+      </c>
+      <c r="I101">
+        <v>18.94</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102" t="s">
+        <v>13</v>
+      </c>
+      <c r="B102" t="s">
+        <v>32</v>
+      </c>
+      <c r="C102">
+        <v>12.1</v>
+      </c>
+      <c r="D102" t="b">
+        <v>0</v>
+      </c>
+      <c r="E102">
+        <v>54.73</v>
+      </c>
+      <c r="F102">
+        <v>49.26</v>
+      </c>
+      <c r="G102">
+        <v>55.8</v>
+      </c>
+      <c r="H102">
+        <v>52.9</v>
+      </c>
+      <c r="I102">
+        <v>27.36</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" t="s">
+        <v>13</v>
+      </c>
+      <c r="B103" t="s">
+        <v>32</v>
+      </c>
+      <c r="C103">
+        <v>12.1</v>
+      </c>
+      <c r="D103" t="b">
+        <v>1</v>
+      </c>
+      <c r="E103">
+        <v>54.73</v>
+      </c>
+      <c r="F103">
+        <v>49.26</v>
+      </c>
+      <c r="G103">
+        <v>60.4</v>
+      </c>
+      <c r="H103">
+        <v>58</v>
+      </c>
+      <c r="I103">
+        <v>27.36</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" t="s">
+        <v>13</v>
+      </c>
+      <c r="B104" t="s">
+        <v>33</v>
+      </c>
+      <c r="C104">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="D104" t="b">
+        <v>0</v>
+      </c>
+      <c r="E104">
+        <v>33.31</v>
+      </c>
+      <c r="F104">
+        <v>29.98</v>
+      </c>
+      <c r="G104">
+        <v>50.4</v>
+      </c>
+      <c r="H104">
+        <v>46.9</v>
+      </c>
+      <c r="I104">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105" t="s">
+        <v>13</v>
+      </c>
+      <c r="B105" t="s">
+        <v>33</v>
+      </c>
+      <c r="C105">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="D105" t="b">
+        <v>1</v>
+      </c>
+      <c r="E105">
+        <v>33.31</v>
+      </c>
+      <c r="F105">
+        <v>29.98</v>
+      </c>
+      <c r="G105">
+        <v>55.9</v>
+      </c>
+      <c r="H105">
+        <v>53</v>
+      </c>
+      <c r="I105">
+        <v>16.66</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106" t="s">
+        <v>13</v>
+      </c>
+      <c r="B106" t="s">
+        <v>34</v>
+      </c>
+      <c r="C106">
+        <v>8.85</v>
+      </c>
+      <c r="D106" t="b">
+        <v>0</v>
+      </c>
+      <c r="E106">
+        <v>35.69</v>
+      </c>
+      <c r="F106">
+        <v>32.12</v>
+      </c>
+      <c r="G106">
+        <v>52.6</v>
+      </c>
+      <c r="H106">
+        <v>49.4</v>
+      </c>
+      <c r="I106">
+        <v>18.83</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
+      <c r="A107" t="s">
+        <v>13</v>
+      </c>
+      <c r="B107" t="s">
+        <v>34</v>
+      </c>
+      <c r="C107">
+        <v>8.85</v>
+      </c>
+      <c r="D107" t="b">
+        <v>1</v>
+      </c>
+      <c r="E107">
+        <v>35.69</v>
+      </c>
+      <c r="F107">
+        <v>32.12</v>
+      </c>
+      <c r="G107">
+        <v>57.8</v>
+      </c>
+      <c r="H107">
+        <v>55.1</v>
+      </c>
+      <c r="I107">
+        <v>17.84</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="A108" t="s">
+        <v>13</v>
+      </c>
+      <c r="B108" t="s">
+        <v>35</v>
+      </c>
+      <c r="C108">
+        <v>6.91</v>
+      </c>
+      <c r="D108" t="b">
+        <v>0</v>
+      </c>
+      <c r="E108">
+        <v>35.69</v>
+      </c>
+      <c r="F108">
+        <v>32.12</v>
+      </c>
+      <c r="G108">
+        <v>59.1</v>
+      </c>
+      <c r="H108">
+        <v>56.5</v>
+      </c>
+      <c r="I108">
+        <v>17.84</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="A109" t="s">
+        <v>13</v>
+      </c>
+      <c r="B109" t="s">
+        <v>35</v>
+      </c>
+      <c r="C109">
+        <v>6.91</v>
+      </c>
+      <c r="D109" t="b">
+        <v>1</v>
+      </c>
+      <c r="E109">
+        <v>35.69</v>
+      </c>
+      <c r="F109">
+        <v>32.12</v>
+      </c>
+      <c r="G109">
+        <v>63.1</v>
+      </c>
+      <c r="H109">
+        <v>61</v>
+      </c>
+      <c r="I109">
+        <v>17.84</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" t="s">
+        <v>13</v>
+      </c>
+      <c r="B110" t="s">
+        <v>36</v>
+      </c>
+      <c r="C110">
+        <v>6.26</v>
+      </c>
+      <c r="D110" t="b">
+        <v>0</v>
+      </c>
+      <c r="E110">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="F110">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="G110">
+        <v>8.1</v>
+      </c>
+      <c r="H110">
+        <v>-1</v>
+      </c>
+      <c r="I110">
+        <v>13.32</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="A111" t="s">
+        <v>13</v>
+      </c>
+      <c r="B111" t="s">
+        <v>36</v>
+      </c>
+      <c r="C111">
+        <v>6.26</v>
+      </c>
+      <c r="D111" t="b">
+        <v>1</v>
+      </c>
+      <c r="E111">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="F111">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="G111">
+        <v>22.4</v>
+      </c>
+      <c r="H111">
+        <v>14.8</v>
+      </c>
+      <c r="I111">
+        <v>9.710000000000001</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="A112" t="s">
+        <v>13</v>
+      </c>
+      <c r="B112" t="s">
+        <v>37</v>
+      </c>
+      <c r="C112">
+        <v>19.72</v>
+      </c>
+      <c r="D112" t="b">
+        <v>0</v>
+      </c>
+      <c r="E112">
+        <v>28.49</v>
+      </c>
+      <c r="F112">
+        <v>25.64</v>
+      </c>
+      <c r="G112">
+        <v>-0.2</v>
+      </c>
+      <c r="H112">
+        <v>-9.4</v>
+      </c>
+      <c r="I112">
+        <v>41.95</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
+      <c r="A113" t="s">
+        <v>13</v>
+      </c>
+      <c r="B113" t="s">
+        <v>37</v>
+      </c>
+      <c r="C113">
+        <v>19.72</v>
+      </c>
+      <c r="D113" t="b">
+        <v>1</v>
+      </c>
+      <c r="E113">
+        <v>28.49</v>
+      </c>
+      <c r="F113">
+        <v>25.64</v>
+      </c>
+      <c r="G113">
+        <v>14.1</v>
+      </c>
+      <c r="H113">
+        <v>6.5</v>
+      </c>
+      <c r="I113">
+        <v>34.68</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
+      <c r="A114" t="s">
+        <v>13</v>
+      </c>
+      <c r="B114" t="s">
+        <v>38</v>
+      </c>
+      <c r="C114">
+        <v>6.26</v>
+      </c>
+      <c r="D114" t="b">
+        <v>0</v>
+      </c>
+      <c r="E114">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="F114">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="G114">
+        <v>8.1</v>
+      </c>
+      <c r="H114">
+        <v>-1</v>
+      </c>
+      <c r="I114">
+        <v>13.32</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
+      <c r="A115" t="s">
+        <v>13</v>
+      </c>
+      <c r="B115" t="s">
+        <v>38</v>
+      </c>
+      <c r="C115">
+        <v>6.26</v>
+      </c>
+      <c r="D115" t="b">
+        <v>1</v>
+      </c>
+      <c r="E115">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="F115">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="G115">
+        <v>22.4</v>
+      </c>
+      <c r="H115">
+        <v>14.8</v>
+      </c>
+      <c r="I115">
+        <v>9.710000000000001</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
+      <c r="A116" t="s">
+        <v>13</v>
+      </c>
+      <c r="B116" t="s">
+        <v>39</v>
+      </c>
+      <c r="C116">
+        <v>19.72</v>
+      </c>
+      <c r="D116" t="b">
+        <v>0</v>
+      </c>
+      <c r="E116">
+        <v>28.49</v>
+      </c>
+      <c r="F116">
+        <v>25.64</v>
+      </c>
+      <c r="G116">
+        <v>-0.2</v>
+      </c>
+      <c r="H116">
+        <v>-9.4</v>
+      </c>
+      <c r="I116">
+        <v>41.95</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
+      <c r="A117" t="s">
+        <v>13</v>
+      </c>
+      <c r="B117" t="s">
+        <v>39</v>
+      </c>
+      <c r="C117">
+        <v>19.72</v>
+      </c>
+      <c r="D117" t="b">
+        <v>1</v>
+      </c>
+      <c r="E117">
+        <v>28.49</v>
+      </c>
+      <c r="F117">
+        <v>25.64</v>
+      </c>
+      <c r="G117">
+        <v>14.1</v>
+      </c>
+      <c r="H117">
+        <v>6.5</v>
+      </c>
+      <c r="I117">
+        <v>34.68</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
+      <c r="A118" t="s">
+        <v>13</v>
+      </c>
+      <c r="B118" t="s">
+        <v>40</v>
+      </c>
+      <c r="C118">
+        <v>6.78</v>
+      </c>
+      <c r="D118" t="b">
+        <v>0</v>
+      </c>
+      <c r="E118">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="F118">
+        <v>8.81</v>
+      </c>
+      <c r="G118">
+        <v>8.1</v>
+      </c>
+      <c r="H118">
+        <v>-1.1</v>
+      </c>
+      <c r="I118">
+        <v>14.43</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
+      <c r="A119" t="s">
+        <v>13</v>
+      </c>
+      <c r="B119" t="s">
+        <v>40</v>
+      </c>
+      <c r="C119">
+        <v>6.78</v>
+      </c>
+      <c r="D119" t="b">
+        <v>1</v>
+      </c>
+      <c r="E119">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="F119">
+        <v>8.81</v>
+      </c>
+      <c r="G119">
+        <v>22.4</v>
+      </c>
+      <c r="H119">
+        <v>14.8</v>
+      </c>
+      <c r="I119">
+        <v>10.52</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
+      <c r="A120" t="s">
+        <v>13</v>
+      </c>
+      <c r="B120" t="s">
+        <v>41</v>
+      </c>
+      <c r="C120">
+        <v>2.5</v>
+      </c>
+      <c r="D120" t="b">
+        <v>0</v>
+      </c>
+      <c r="E120">
+        <v>3.61</v>
+      </c>
+      <c r="F120">
+        <v>3.25</v>
+      </c>
+      <c r="G120">
+        <v>8.1</v>
+      </c>
+      <c r="H120">
+        <v>-1.1</v>
+      </c>
+      <c r="I120">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
+      <c r="A121" t="s">
+        <v>13</v>
+      </c>
+      <c r="B121" t="s">
+        <v>41</v>
+      </c>
+      <c r="C121">
+        <v>2.5</v>
+      </c>
+      <c r="D121" t="b">
+        <v>1</v>
+      </c>
+      <c r="E121">
+        <v>3.61</v>
+      </c>
+      <c r="F121">
+        <v>3.25</v>
+      </c>
+      <c r="G121">
+        <v>22.4</v>
+      </c>
+      <c r="H121">
+        <v>14.8</v>
+      </c>
+      <c r="I121">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
+      <c r="A122" t="s">
+        <v>13</v>
+      </c>
+      <c r="B122" t="s">
+        <v>42</v>
+      </c>
+      <c r="C122">
+        <v>6.55</v>
+      </c>
+      <c r="D122" t="b">
+        <v>0</v>
+      </c>
+      <c r="E122">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="F122">
+        <v>8.52</v>
+      </c>
+      <c r="G122">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H122">
+        <v>-1</v>
+      </c>
+      <c r="I122">
+        <v>13.94</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
+      <c r="A123" t="s">
+        <v>13</v>
+      </c>
+      <c r="B123" t="s">
+        <v>42</v>
+      </c>
+      <c r="C123">
+        <v>6.55</v>
+      </c>
+      <c r="D123" t="b">
+        <v>1</v>
+      </c>
+      <c r="E123">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="F123">
+        <v>8.52</v>
+      </c>
+      <c r="G123">
+        <v>22.5</v>
+      </c>
+      <c r="H123">
+        <v>14.9</v>
+      </c>
+      <c r="I123">
+        <v>10.15</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
+      <c r="A124" t="s">
+        <v>13</v>
+      </c>
+      <c r="B124" t="s">
+        <v>43</v>
+      </c>
+      <c r="C124">
+        <v>9.92</v>
+      </c>
+      <c r="D124" t="b">
+        <v>0</v>
+      </c>
+      <c r="E124">
+        <v>35.69</v>
+      </c>
+      <c r="F124">
+        <v>32.12</v>
+      </c>
+      <c r="G124">
+        <v>49.1</v>
+      </c>
+      <c r="H124">
+        <v>45.4</v>
+      </c>
+      <c r="I124">
+        <v>21.11</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
+      <c r="A125" t="s">
+        <v>13</v>
+      </c>
+      <c r="B125" t="s">
+        <v>43</v>
+      </c>
+      <c r="C125">
+        <v>9.92</v>
+      </c>
+      <c r="D125" t="b">
+        <v>1</v>
+      </c>
+      <c r="E125">
+        <v>35.69</v>
+      </c>
+      <c r="F125">
+        <v>32.12</v>
+      </c>
+      <c r="G125">
+        <v>54.8</v>
+      </c>
+      <c r="H125">
+        <v>51.8</v>
+      </c>
+      <c r="I125">
+        <v>17.84</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
+      <c r="A126" t="s">
+        <v>13</v>
+      </c>
+      <c r="B126" t="s">
+        <v>44</v>
+      </c>
+      <c r="C126">
+        <v>3</v>
+      </c>
+      <c r="D126" t="b">
+        <v>0</v>
+      </c>
+      <c r="E126">
+        <v>26.17</v>
+      </c>
+      <c r="F126">
+        <v>23.55</v>
+      </c>
+      <c r="G126">
+        <v>68.5</v>
+      </c>
+      <c r="H126">
+        <v>67</v>
+      </c>
+      <c r="I126">
+        <v>13.09</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
+      <c r="A127" t="s">
+        <v>13</v>
+      </c>
+      <c r="B127" t="s">
+        <v>44</v>
+      </c>
+      <c r="C127">
+        <v>3</v>
+      </c>
+      <c r="D127" t="b">
+        <v>1</v>
+      </c>
+      <c r="E127">
+        <v>26.17</v>
+      </c>
+      <c r="F127">
+        <v>23.55</v>
+      </c>
+      <c r="G127">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="H127">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="I127">
+        <v>13.09</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
+      <c r="A128" t="s">
+        <v>13</v>
+      </c>
+      <c r="B128" t="s">
+        <v>45</v>
+      </c>
+      <c r="C128">
+        <v>7.98</v>
+      </c>
+      <c r="D128" t="b">
+        <v>0</v>
+      </c>
+      <c r="E128">
+        <v>33.5</v>
+      </c>
+      <c r="F128">
+        <v>30.15</v>
+      </c>
+      <c r="G128">
+        <v>53.8</v>
+      </c>
+      <c r="H128">
+        <v>50.7</v>
+      </c>
+      <c r="I128">
+        <v>16.98</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
+      <c r="A129" t="s">
+        <v>13</v>
+      </c>
+      <c r="B129" t="s">
+        <v>45</v>
+      </c>
+      <c r="C129">
+        <v>7.98</v>
+      </c>
+      <c r="D129" t="b">
+        <v>1</v>
+      </c>
+      <c r="E129">
+        <v>33.5</v>
+      </c>
+      <c r="F129">
+        <v>30.15</v>
+      </c>
+      <c r="G129">
+        <v>58.7</v>
+      </c>
+      <c r="H129">
+        <v>56.1</v>
+      </c>
+      <c r="I129">
+        <v>16.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>